--- a/languages/es/output/import/西班牙语专八高阶.xlsx
+++ b/languages/es/output/import/西班牙语专八高阶.xlsx
@@ -22295,7 +22295,7 @@
       </c>
       <c r="B686" s="1" t="inlineStr">
         <is>
-          <t>[ˈmanɡo] 芒果&lt;名&gt;</t>
+          <t>[ˈmanɡo] 柄；把手&lt;名&gt;</t>
         </is>
       </c>
       <c r="C686" s="1" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="D686" s="1" t="inlineStr">
         <is>
-          <t>芒果</t>
+          <t>柄；把手</t>
         </is>
       </c>
       <c r="E686" s="1" t="inlineStr">
@@ -35779,7 +35779,7 @@
       </c>
       <c r="B1109" s="1" t="inlineStr">
         <is>
-          <t>[fabɾiˈkaɾ] 制造&lt;动&gt;</t>
+          <t>[fabɾiˈkaɾ] 制造；生产&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1109" s="1" t="inlineStr">
@@ -35789,7 +35789,7 @@
       </c>
       <c r="D1109" s="1" t="inlineStr">
         <is>
-          <t>制造</t>
+          <t>制造；生产</t>
         </is>
       </c>
       <c r="E1109" s="1" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="B1187" s="1" t="inlineStr">
         <is>
-          <t>[aboɾˈdaɾ] 地址&lt;动&gt;</t>
+          <t>[aboɾˈdaɾ] 处理；着手(问题)&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1187" s="1" t="inlineStr">
@@ -38277,7 +38277,7 @@
       </c>
       <c r="D1187" s="1" t="inlineStr">
         <is>
-          <t>地址</t>
+          <t>处理；着手(问题)</t>
         </is>
       </c>
       <c r="E1187" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专八高阶.xlsx
+++ b/languages/es/output/import/西班牙语专八高阶.xlsx
@@ -36255,7 +36255,7 @@
       </c>
       <c r="B1124" s="1" t="inlineStr">
         <is>
-          <t>[etˈθeteɾa/ [et̪ˈθe.t̪e.ɾa]] 等等&lt;名&gt;</t>
+          <t>[etˈθeteɾa] 等等&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1124" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专八高阶.xlsx
+++ b/languages/es/output/import/西班牙语专八高阶.xlsx
@@ -21979,7 +21979,7 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>[ˈkas] CAS&lt;名&gt;</t>
+          <t>[ˈkas] 化学文摘社号；CAS登记号&lt;名&gt;</t>
         </is>
       </c>
       <c r="C676" s="1" t="inlineStr">
@@ -21989,7 +21989,7 @@
       </c>
       <c r="D676" s="1" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>化学文摘社号</t>
         </is>
       </c>
       <c r="E676" s="1" t="inlineStr">

--- a/languages/es/output/import/西班牙语专八高阶.xlsx
+++ b/languages/es/output/import/西班牙语专八高阶.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>[sospeˈt͡ʃaɾ] 嫌疑人&lt;动&gt;</t>
+          <t>[/sospeˈt͡ʃaɾ/] 怀疑；猜疑&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>嫌疑人</t>
+          <t>怀疑；猜疑</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>[biˈbjente] 生活&lt;名&gt;</t>
+          <t>[/biˈbjente/] 活着的；在世的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>生活</t>
+          <t>活着的；在世的</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>[ˈtopo] 摩尔&lt;名&gt;</t>
+          <t>[/ˈtopo/] 鼹鼠&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>摩尔</t>
+          <t>鼹鼠</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1398,7 +1398,11 @@
           <t>金融&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>/finanˈθjeɾa/</t>
+        </is>
+      </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
           <t>金融</t>
@@ -1423,7 +1427,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>[peˈnal] 罪犯&lt;名&gt;</t>
+          <t>[/peˈnal/] 刑事的&lt;形&gt;；点球&lt;名&gt;；监狱&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1433,7 +1437,7 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>罪犯</t>
+          <t>刑事的&lt;形&gt;；点球&lt;名&gt;；监狱&lt;名&gt;</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
@@ -1615,7 +1619,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>[resˈpaldo] 备份&lt;名&gt;</t>
+          <t>[/resˈpaldo/] 支持&lt;名&gt;；靠背&lt;名&gt;；背后支持&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1625,7 +1629,7 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>备份</t>
+          <t>支持&lt;名&gt;；靠背&lt;名&gt;；背后支持&lt;名&gt;</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1775,7 +1779,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>[leˈxitimo] 合法的&lt;形&gt;</t>
+          <t>[/leˈxitimo/] 合法的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>合法的</t>
+          <t>合法的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>[pɾoɡɾaˈmaɾ] 时间表&lt;动&gt;</t>
+          <t>[/pɾoɡɾaˈmaɾ/] 编程；安排；计划&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2137,7 +2141,7 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>时间表</t>
+          <t>编程；安排；计划</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -3247,7 +3251,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>[aˈdema] 除此之外&lt;名&gt;</t>
+          <t>[aˈdema] 修枝刀；钩刀&lt;名&gt;</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3257,7 +3261,7 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>除此之外</t>
+          <t>修枝刀；钩刀</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -3634,7 +3638,11 @@
           <t>维罗妮卡&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr"/>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>/beˈɾonika/</t>
+        </is>
+      </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
           <t>维罗妮卡</t>
@@ -3662,7 +3670,11 @@
           <t>法语&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr"/>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>/fɾˈanθes/</t>
+        </is>
+      </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
           <t>法语</t>
@@ -3815,7 +3827,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>[senˈdeɾo] 踪迹&lt;名&gt;</t>
+          <t>[senˈdeɾo] 小路；小径&lt;名&gt;</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3825,7 +3837,7 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>踪迹</t>
+          <t>小路；小径</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -3847,7 +3859,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>[aɾteˈfaɡto] 神器&lt;名&gt;</t>
+          <t>[aɾteˈfaɡto] 人工制品；装置；器械&lt;名&gt;</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3857,7 +3869,7 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>神器</t>
+          <t>人工制品；装置；器械</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -3879,7 +3891,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>[ˈkant͡ʃa] 法庭&lt;名&gt;</t>
+          <t>[ˈkant͡ʃa] 球场；场地&lt;名&gt;</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3889,7 +3901,7 @@
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>法庭</t>
+          <t>球场；场地</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -4103,7 +4115,7 @@
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>[laˈtiɾ] 击败&lt;动&gt;</t>
+          <t>[laˈtiɾ] 跳动；搏动&lt;动&gt;</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -4113,7 +4125,7 @@
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>击败</t>
+          <t>跳动；搏动</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
@@ -4362,7 +4374,11 @@
           <t>三明治&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr"/>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>/sandwˈitʃ/</t>
+        </is>
+      </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
           <t>三明治</t>
@@ -4739,7 +4755,7 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>[koˈrea] 表带&lt;名&gt;</t>
+          <t>[/koˈrea/] 皮带；带子&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4749,7 +4765,7 @@
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>皮带；带子&lt;名&gt;</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -6179,13 +6195,17 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>君&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C181" s="1" t="inlineStr"/>
+          <t>六月&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>/xˈun/</t>
+        </is>
+      </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>君</t>
+          <t>六月</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -6431,7 +6451,7 @@
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>[esˈpjaɾ] 间谍&lt;动&gt;</t>
+          <t>[esˈpjaɾ] 窥探；侦察；监视&lt;动&gt;</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -6441,7 +6461,7 @@
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>间谍</t>
+          <t>窥探；侦察；监视</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
@@ -6815,7 +6835,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>[foɾˈθaɾ] 力&lt;动&gt;</t>
+          <t>[foɾˈθaɾ] 强迫；强制；强行打开&lt;动&gt;</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -6825,7 +6845,7 @@
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>力</t>
+          <t>强迫；强制；强行打开</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -7327,7 +7347,7 @@
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>[afɾonˈtaɾ] 脸&lt;动&gt;</t>
+          <t>[afɾonˈtaɾ] 面对；面临；正视&lt;动&gt;</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -7337,7 +7357,7 @@
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>脸</t>
+          <t>面对；面临；正视</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
@@ -7583,7 +7603,7 @@
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>[kliˈbaɾ] 劈开&lt;动&gt;</t>
+          <t>[/kliˈbaɾ/] 钉；钉住&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -7593,7 +7613,7 @@
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>劈开</t>
+          <t>钉；钉住</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
@@ -8191,7 +8211,7 @@
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>[ˈsweɡɾa] 婆婆&lt;名&gt;</t>
+          <t>[/ˈsweɡɾa/] 岳母；婆婆&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
@@ -8201,7 +8221,7 @@
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>婆婆</t>
+          <t>岳母；婆婆</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
@@ -8223,7 +8243,7 @@
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>[θeˈdeɾ] 产量&lt;动&gt;</t>
+          <t>[θeˈdeɾ] 让与；转让；让步&lt;动&gt;</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -8233,7 +8253,7 @@
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>产量</t>
+          <t>让与；转让；让步</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
@@ -9375,7 +9395,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>[boˈrado] 被抹去&lt;名&gt;</t>
+          <t>[/boˈrado/] 被删除的；删除&lt;形/分词&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -9385,7 +9405,7 @@
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>被抹去</t>
+          <t>被删除的；删除&lt;形/分词&gt;</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
@@ -10015,7 +10035,7 @@
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>[ˈdese] 欲望&lt;名&gt;</t>
+          <t>[/ˈdese/] dar的虚拟式/敬语命令式形式（如 déselo）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
@@ -10025,7 +10045,7 @@
       </c>
       <c r="D301" s="1" t="inlineStr">
         <is>
-          <t>欲望</t>
+          <t>dar的虚拟式/敬语命令式形式（如 déselo）</t>
         </is>
       </c>
       <c r="E301" s="1" t="inlineStr">
@@ -10463,7 +10483,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>[demanˈdaɾ] 苏&lt;动&gt;</t>
+          <t>[demanˈdaɾ] 控告；起诉；要求&lt;动&gt;</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -10473,7 +10493,7 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t>苏</t>
+          <t>控告；起诉；要求</t>
         </is>
       </c>
       <c r="E315" s="1" t="inlineStr">
@@ -10559,7 +10579,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>[ˈmae] 梅埃&lt;名&gt;</t>
+          <t>[/ˈmae/] 老兄（哥斯达黎加俚语）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
@@ -10569,7 +10589,7 @@
       </c>
       <c r="D318" s="1" t="inlineStr">
         <is>
-          <t>梅埃</t>
+          <t>老兄（哥斯达黎加俚语）</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
@@ -10719,7 +10739,7 @@
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>[adeˈlanto] 提前&lt;名&gt;</t>
+          <t>[/adeˈlanto/] 进步，进展；预告；预支&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
@@ -10729,7 +10749,7 @@
       </c>
       <c r="D323" s="1" t="inlineStr">
         <is>
-          <t>提前</t>
+          <t>进步，进展；预告；预支</t>
         </is>
       </c>
       <c r="E323" s="1" t="inlineStr">
@@ -11167,7 +11187,7 @@
       </c>
       <c r="B337" s="1" t="inlineStr">
         <is>
-          <t>[ˈboɾda] 落水&lt;名&gt;</t>
+          <t>[ˈboɾda] 牧人小屋；山间棚屋&lt;名&gt;</t>
         </is>
       </c>
       <c r="C337" s="1" t="inlineStr">
@@ -11177,7 +11197,7 @@
       </c>
       <c r="D337" s="1" t="inlineStr">
         <is>
-          <t>落水</t>
+          <t>牧人小屋；山间棚屋</t>
         </is>
       </c>
       <c r="E337" s="1" t="inlineStr">
@@ -11455,7 +11475,7 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>[ˈdea] 德阿&lt;名&gt;</t>
+          <t>[ˈdea] 女神&lt;名&gt;</t>
         </is>
       </c>
       <c r="C346" s="1" t="inlineStr">
@@ -11465,7 +11485,7 @@
       </c>
       <c r="D346" s="1" t="inlineStr">
         <is>
-          <t>德阿</t>
+          <t>女神</t>
         </is>
       </c>
       <c r="E346" s="1" t="inlineStr">
@@ -11519,7 +11539,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>[nomˈbɾaɾ] 姓名&lt;动&gt;</t>
+          <t>[nomˈbɾaɾ] 命名；任命；提及&lt;动&gt;</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -11529,7 +11549,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>姓名</t>
+          <t>命名；任命；提及</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -11583,7 +11603,7 @@
       </c>
       <c r="B350" s="1" t="inlineStr">
         <is>
-          <t>[asamˈblea] 组装&lt;名&gt;</t>
+          <t>[/asamˈblea/] 大会；会议；集会&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C350" s="1" t="inlineStr">
@@ -11593,7 +11613,7 @@
       </c>
       <c r="D350" s="1" t="inlineStr">
         <is>
-          <t>组装</t>
+          <t>大会；会议；集会</t>
         </is>
       </c>
       <c r="E350" s="1" t="inlineStr">
@@ -12031,7 +12051,7 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>[despeɾdiˈθjaɾ] 废物&lt;动&gt;</t>
+          <t>[/despeɾdiˈθjaɾ/] 浪费&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C364" s="1" t="inlineStr">
@@ -12041,7 +12061,7 @@
       </c>
       <c r="D364" s="1" t="inlineStr">
         <is>
-          <t>废物</t>
+          <t>浪费</t>
         </is>
       </c>
       <c r="E364" s="1" t="inlineStr">
@@ -12322,7 +12342,11 @@
           <t>值得&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C373" s="1" t="inlineStr"/>
+      <c r="C373" s="1" t="inlineStr">
+        <is>
+          <t>/ˈdiɡna/</t>
+        </is>
+      </c>
       <c r="D373" s="1" t="inlineStr">
         <is>
           <t>值得</t>
@@ -12731,7 +12755,7 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>[inˈdjana] 印第安纳州&lt;名&gt;</t>
+          <t>[/inˈdjana/] 印第安的；印第安女子&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
@@ -12741,7 +12765,7 @@
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t>印第安纳州</t>
+          <t>印第安的；印第安女子</t>
         </is>
       </c>
       <c r="E386" s="1" t="inlineStr">
@@ -12859,7 +12883,7 @@
       </c>
       <c r="B390" s="1" t="inlineStr">
         <is>
-          <t>[ˈrait] 对&lt;名&gt;</t>
+          <t>[/ˈrait/] 权利；右边；正确&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C390" s="1" t="inlineStr">
@@ -12869,7 +12893,7 @@
       </c>
       <c r="D390" s="1" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>权利；右边；正确</t>
         </is>
       </c>
       <c r="E390" s="1" t="inlineStr">
@@ -12894,7 +12918,11 @@
           <t>封面&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C391" s="1" t="inlineStr"/>
+      <c r="C391" s="1" t="inlineStr">
+        <is>
+          <t>/tapaˈðeɾa/</t>
+        </is>
+      </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
           <t>封面</t>
@@ -13335,7 +13363,7 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>[ˈpo] 婆&lt;叹&gt;</t>
+          <t>[/ˈpo/] 嗯；呀（叹词）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
@@ -13345,7 +13373,7 @@
       </c>
       <c r="D405" s="1" t="inlineStr">
         <is>
-          <t>婆</t>
+          <t>嗯；呀（叹词）</t>
         </is>
       </c>
       <c r="E405" s="1" t="inlineStr">
@@ -14423,7 +14451,7 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>[aˈtaɾ] 领带&lt;动&gt;</t>
+          <t>[/aˈtaɾ/] 系；绑；捆&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C439" s="1" t="inlineStr">
@@ -14433,7 +14461,7 @@
       </c>
       <c r="D439" s="1" t="inlineStr">
         <is>
-          <t>领带</t>
+          <t>系；绑；捆</t>
         </is>
       </c>
       <c r="E439" s="1" t="inlineStr">
@@ -14775,7 +14803,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>[plaˈneo] 我计划&lt;名&gt;</t>
+          <t>[/plaˈneo/] 滑翔；滑行&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
@@ -14785,7 +14813,7 @@
       </c>
       <c r="D450" s="1" t="inlineStr">
         <is>
-          <t>我计划</t>
+          <t>滑翔；滑行</t>
         </is>
       </c>
       <c r="E450" s="1" t="inlineStr">
@@ -14871,7 +14899,7 @@
       </c>
       <c r="B453" s="1" t="inlineStr">
         <is>
-          <t>[tɾaˈɡaɾ] 燕子&lt;动&gt;</t>
+          <t>[/tɾaˈɡaɾ/] 吞下；咽下&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C453" s="1" t="inlineStr">
@@ -14881,7 +14909,7 @@
       </c>
       <c r="D453" s="1" t="inlineStr">
         <is>
-          <t>燕子</t>
+          <t>吞下；咽下</t>
         </is>
       </c>
       <c r="E453" s="1" t="inlineStr">
@@ -15162,7 +15190,11 @@
           <t>法拉利&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C462" s="1" t="inlineStr"/>
+      <c r="C462" s="1" t="inlineStr">
+        <is>
+          <t>/ferˈaɾi/</t>
+        </is>
+      </c>
       <c r="D462" s="1" t="inlineStr">
         <is>
           <t>法拉利</t>
@@ -15347,7 +15379,7 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>[enˈtɾaɲa] 需要&lt;名&gt;</t>
+          <t>[/enˈtɾaɲa/] 内脏；内心&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C468" s="1" t="inlineStr">
@@ -15357,7 +15389,7 @@
       </c>
       <c r="D468" s="1" t="inlineStr">
         <is>
-          <t>需要</t>
+          <t>内脏；内心</t>
         </is>
       </c>
       <c r="E468" s="1" t="inlineStr">
@@ -15443,7 +15475,7 @@
       </c>
       <c r="B471" s="1" t="inlineStr">
         <is>
-          <t>[ˈw̝en] 当&lt;连&gt;</t>
+          <t>[/ˈw̝en/] 什么时候；当…时&lt;conj&gt;</t>
         </is>
       </c>
       <c r="C471" s="1" t="inlineStr">
@@ -15453,7 +15485,7 @@
       </c>
       <c r="D471" s="1" t="inlineStr">
         <is>
-          <t>当</t>
+          <t>什么时候；当…时</t>
         </is>
       </c>
       <c r="E471" s="1" t="inlineStr">
@@ -15510,7 +15542,11 @@
           <t>微波炉&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C473" s="1" t="inlineStr"/>
+      <c r="C473" s="1" t="inlineStr">
+        <is>
+          <t>/mikɾoondas/</t>
+        </is>
+      </c>
       <c r="D473" s="1" t="inlineStr">
         <is>
           <t>微波炉</t>
@@ -15631,7 +15667,7 @@
       </c>
       <c r="B477" s="1" t="inlineStr">
         <is>
-          <t>[ˈta] 塔&lt;动&gt;</t>
+          <t>[/ˈta/] （口语）好的；行&lt;叹&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C477" s="1" t="inlineStr">
@@ -15641,7 +15677,7 @@
       </c>
       <c r="D477" s="1" t="inlineStr">
         <is>
-          <t>塔</t>
+          <t>（口语）好的；行&lt;叹&gt;</t>
         </is>
       </c>
       <c r="E477" s="1" t="inlineStr">
@@ -17039,7 +17075,7 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>[ˈpope] 教皇&lt;名&gt;</t>
+          <t>[/ˈpope/] 教皇&lt;名&gt;（西语应为 papa）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C521" s="1" t="inlineStr">
@@ -17049,7 +17085,7 @@
       </c>
       <c r="D521" s="1" t="inlineStr">
         <is>
-          <t>教皇</t>
+          <t>教皇&lt;名&gt;（西语应为 papa）</t>
         </is>
       </c>
       <c r="E521" s="1" t="inlineStr">
@@ -17138,7 +17174,11 @@
           <t>坐&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C524" s="1" t="inlineStr"/>
+      <c r="C524" s="1" t="inlineStr">
+        <is>
+          <t>/sientˈate/</t>
+        </is>
+      </c>
       <c r="D524" s="1" t="inlineStr">
         <is>
           <t>坐</t>
@@ -17518,7 +17558,11 @@
           <t>记录&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C536" s="1" t="inlineStr"/>
+      <c r="C536" s="1" t="inlineStr">
+        <is>
+          <t>/ɾekˈoɾd/</t>
+        </is>
+      </c>
       <c r="D536" s="1" t="inlineStr">
         <is>
           <t>记录</t>
@@ -18023,7 +18067,7 @@
       </c>
       <c r="B552" s="1" t="inlineStr">
         <is>
-          <t>[suˈdaɾ] 汗水&lt;动&gt;</t>
+          <t>[/suˈdaɾ/] 出汗；流汗&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C552" s="1" t="inlineStr">
@@ -18033,7 +18077,7 @@
       </c>
       <c r="D552" s="1" t="inlineStr">
         <is>
-          <t>汗水</t>
+          <t>出汗；流汗</t>
         </is>
       </c>
       <c r="E552" s="1" t="inlineStr">
@@ -18375,7 +18419,7 @@
       </c>
       <c r="B563" s="1" t="inlineStr">
         <is>
-          <t>[ˈseo] 搜索引擎优化&lt;名&gt;</t>
+          <t>[/ˈseo/] 大教堂；主教座堂&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C563" s="1" t="inlineStr">
@@ -18385,7 +18429,7 @@
       </c>
       <c r="D563" s="1" t="inlineStr">
         <is>
-          <t>搜索引擎优化</t>
+          <t>大教堂；主教座堂&lt;名&gt;</t>
         </is>
       </c>
       <c r="E563" s="1" t="inlineStr">
@@ -18663,7 +18707,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>[paˈtan] 奥夫&lt;名&gt;</t>
+          <t>[/paˈtan/] 乡巴佬；粗人&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C572" s="1" t="inlineStr">
@@ -18673,7 +18717,7 @@
       </c>
       <c r="D572" s="1" t="inlineStr">
         <is>
-          <t>奥夫</t>
+          <t>乡巴佬；粗人</t>
         </is>
       </c>
       <c r="E572" s="1" t="inlineStr">
@@ -18855,7 +18899,7 @@
       </c>
       <c r="B578" s="1" t="inlineStr">
         <is>
-          <t>[pɾoθeˈsaɾ] 过程&lt;动&gt;</t>
+          <t>[/pɾoθeˈsaɾ/] 处理；加工&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C578" s="1" t="inlineStr">
@@ -18865,7 +18909,7 @@
       </c>
       <c r="D578" s="1" t="inlineStr">
         <is>
-          <t>过程</t>
+          <t>处理；加工</t>
         </is>
       </c>
       <c r="E578" s="1" t="inlineStr">
@@ -19057,7 +19101,7 @@
       </c>
       <c r="D584" s="1" t="inlineStr">
         <is>
-          <t>线</t>
+          <t>英语词，非西班牙语；应为 línea（线）</t>
         </is>
       </c>
       <c r="E584" s="1" t="inlineStr">
@@ -19079,7 +19123,7 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>[rasˈɡuɲo] 从头开始&lt;名&gt;</t>
+          <t>[/rasˈɡuɲo/] 抓痕；划伤&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C585" s="1" t="inlineStr">
@@ -19089,7 +19133,7 @@
       </c>
       <c r="D585" s="1" t="inlineStr">
         <is>
-          <t>从头开始</t>
+          <t>抓痕；划伤</t>
         </is>
       </c>
       <c r="E585" s="1" t="inlineStr">
@@ -19146,7 +19190,11 @@
           <t>大&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C587" s="1" t="inlineStr"/>
+      <c r="C587" s="1" t="inlineStr">
+        <is>
+          <t>/ɡɾanˈdote/</t>
+        </is>
+      </c>
       <c r="D587" s="1" t="inlineStr">
         <is>
           <t>大</t>
@@ -19430,7 +19478,11 @@
           <t>等等&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C596" s="1" t="inlineStr"/>
+      <c r="C596" s="1" t="inlineStr">
+        <is>
+          <t>/etk/</t>
+        </is>
+      </c>
       <c r="D596" s="1" t="inlineStr">
         <is>
           <t>等等</t>
@@ -19583,7 +19635,7 @@
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
-          <t>[peˈʝexo] 隐藏&lt;名&gt;</t>
+          <t>[/peˈʝexo/] 皮肤；兽皮&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C601" s="1" t="inlineStr">
@@ -19593,7 +19645,7 @@
       </c>
       <c r="D601" s="1" t="inlineStr">
         <is>
-          <t>隐藏</t>
+          <t>皮肤；兽皮</t>
         </is>
       </c>
       <c r="E601" s="1" t="inlineStr">
@@ -19967,7 +20019,7 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>[planˈtaɾ] 植物&lt;动&gt;</t>
+          <t>[/planˈtaɾ/] 种植；栽种&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C613" s="1" t="inlineStr">
@@ -19977,7 +20029,7 @@
       </c>
       <c r="D613" s="1" t="inlineStr">
         <is>
-          <t>植物</t>
+          <t>种植；栽种</t>
         </is>
       </c>
       <c r="E613" s="1" t="inlineStr">
@@ -20287,7 +20339,7 @@
       </c>
       <c r="B623" s="1" t="inlineStr">
         <is>
-          <t>[tituˈlaɾ] 持有人&lt;名&gt;</t>
+          <t>[/tituˈlaɾ/] 持有，拥有；冠以标题&lt;动&gt;；持有人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C623" s="1" t="inlineStr">
@@ -20297,7 +20349,7 @@
       </c>
       <c r="D623" s="1" t="inlineStr">
         <is>
-          <t>持有人</t>
+          <t>持有，拥有；冠以标题&lt;动&gt;；持有人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E623" s="1" t="inlineStr">
@@ -20319,7 +20371,7 @@
       </c>
       <c r="B624" s="1" t="inlineStr">
         <is>
-          <t>[ʝaˈθeɾ] 谎言&lt;动&gt;</t>
+          <t>[/ʝaˈθeɾ/] 躺；卧；安息&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C624" s="1" t="inlineStr">
@@ -20329,7 +20381,7 @@
       </c>
       <c r="D624" s="1" t="inlineStr">
         <is>
-          <t>谎言</t>
+          <t>躺；卧；安息</t>
         </is>
       </c>
       <c r="E624" s="1" t="inlineStr">
@@ -20639,7 +20691,7 @@
       </c>
       <c r="B634" s="1" t="inlineStr">
         <is>
-          <t>[reˈkoɾte] 剪纸&lt;名&gt;</t>
+          <t>[/reˈkoɾte/] 剪下；剪报，剪下的碎片&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C634" s="1" t="inlineStr">
@@ -20649,7 +20701,7 @@
       </c>
       <c r="D634" s="1" t="inlineStr">
         <is>
-          <t>剪纸</t>
+          <t>剪下；剪报，剪下的碎片&lt;名&gt;</t>
         </is>
       </c>
       <c r="E634" s="1" t="inlineStr">
@@ -21439,7 +21491,7 @@
       </c>
       <c r="B659" s="1" t="inlineStr">
         <is>
-          <t>[pɾesidenˈθjal] 总统&lt;形&gt;</t>
+          <t>[/pɾesidenˈθjal/] 总统的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C659" s="1" t="inlineStr">
@@ -21449,7 +21501,7 @@
       </c>
       <c r="D659" s="1" t="inlineStr">
         <is>
-          <t>总统</t>
+          <t>总统的</t>
         </is>
       </c>
       <c r="E659" s="1" t="inlineStr">
@@ -21567,13 +21619,17 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>凸起&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C663" s="1" t="inlineStr"/>
+          <t>[[kɾiˈo] 抚养；养育&lt;verb&gt;</t>
+        </is>
+      </c>
+      <c r="C663" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkɾio/</t>
+        </is>
+      </c>
       <c r="D663" s="1" t="inlineStr">
         <is>
-          <t>凸起</t>
+          <t>抚养；养育</t>
         </is>
       </c>
       <c r="E663" s="1" t="inlineStr">
@@ -21979,7 +22035,7 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>[ˈkas] 化学文摘社号；CAS登记号&lt;名&gt;</t>
+          <t>[/ˈkas/] 房屋；家（casa 的缩写）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C676" s="1" t="inlineStr">
@@ -21989,7 +22045,7 @@
       </c>
       <c r="D676" s="1" t="inlineStr">
         <is>
-          <t>化学文摘社号</t>
+          <t>房屋；家（casa 的缩写）</t>
         </is>
       </c>
       <c r="E676" s="1" t="inlineStr">
@@ -22011,7 +22067,7 @@
       </c>
       <c r="B677" s="1" t="inlineStr">
         <is>
-          <t>[ˈpum] 繁荣&lt;叹&gt;</t>
+          <t>[/ˈpum/] 砰（拟声词）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C677" s="1" t="inlineStr">
@@ -22021,7 +22077,7 @@
       </c>
       <c r="D677" s="1" t="inlineStr">
         <is>
-          <t>繁荣</t>
+          <t>砰（拟声词）</t>
         </is>
       </c>
       <c r="E677" s="1" t="inlineStr">
@@ -22142,7 +22198,11 @@
           <t>绝地武士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C681" s="1" t="inlineStr"/>
+      <c r="C681" s="1" t="inlineStr">
+        <is>
+          <t>/xˈedi/</t>
+        </is>
+      </c>
       <c r="D681" s="1" t="inlineStr">
         <is>
           <t>绝地武士</t>
@@ -22199,7 +22259,7 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>[manifestaˈθjon] 示范&lt;名&gt;</t>
+          <t>[/manifestaˈθjon/] 示威游行；表明；显示&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C683" s="1" t="inlineStr">
@@ -22209,7 +22269,7 @@
       </c>
       <c r="D683" s="1" t="inlineStr">
         <is>
-          <t>示范</t>
+          <t>示威游行；表明；显示</t>
         </is>
       </c>
       <c r="E683" s="1" t="inlineStr">
@@ -22327,7 +22387,7 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>[onˈraɾ] 荣誉&lt;动&gt;</t>
+          <t>[/onˈraɾ/] 尊敬；给…以荣誉&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C687" s="1" t="inlineStr">
@@ -22337,7 +22397,7 @@
       </c>
       <c r="D687" s="1" t="inlineStr">
         <is>
-          <t>荣誉</t>
+          <t>尊敬；给…以荣誉</t>
         </is>
       </c>
       <c r="E687" s="1" t="inlineStr">
@@ -22551,7 +22611,7 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>[ˈimno] 国歌&lt;名&gt;</t>
+          <t>[/ˈimno/] 圣歌，颂歌；国歌&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C694" s="1" t="inlineStr">
@@ -22561,7 +22621,7 @@
       </c>
       <c r="D694" s="1" t="inlineStr">
         <is>
-          <t>国歌</t>
+          <t>圣歌，颂歌；国歌&lt;名&gt;</t>
         </is>
       </c>
       <c r="E694" s="1" t="inlineStr">
@@ -22593,7 +22653,7 @@
       </c>
       <c r="D695" s="1" t="inlineStr">
         <is>
-          <t>好</t>
+          <t>（非西班牙语词，西语应为buen）好&lt;形&gt;</t>
         </is>
       </c>
       <c r="E695" s="1" t="inlineStr">
@@ -22775,13 +22835,17 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>铁托&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C701" s="1" t="inlineStr"/>
+          <t>[[ˈtito]] 叔叔&lt;名&gt;（对父亲朋友的昵称）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C701" s="1" t="inlineStr">
+        <is>
+          <t>/tito/</t>
+        </is>
+      </c>
       <c r="D701" s="1" t="inlineStr">
         <is>
-          <t>铁托</t>
+          <t>叔叔&lt;名&gt;（对父亲朋友的昵称）</t>
         </is>
       </c>
       <c r="E701" s="1" t="inlineStr">
@@ -22803,7 +22867,7 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>[eɡsˈpɾeso] 快递&lt;名&gt;</t>
+          <t>[/eɡsˈpɾeso/] 快的&lt;形&gt;；特快列车&lt;名&gt;；浓缩咖啡&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C702" s="1" t="inlineStr">
@@ -22813,7 +22877,7 @@
       </c>
       <c r="D702" s="1" t="inlineStr">
         <is>
-          <t>快递</t>
+          <t>快的&lt;形&gt;；特快列车&lt;名&gt;；浓缩咖啡&lt;名&gt;</t>
         </is>
       </c>
       <c r="E702" s="1" t="inlineStr">
@@ -23027,7 +23091,7 @@
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>[koreˈxiɾ] 正确&lt;动&gt;</t>
+          <t>[/koreˈxiɾ/] 改正；纠正&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C709" s="1" t="inlineStr">
@@ -23037,7 +23101,7 @@
       </c>
       <c r="D709" s="1" t="inlineStr">
         <is>
-          <t>正确</t>
+          <t>改正；纠正</t>
         </is>
       </c>
       <c r="E709" s="1" t="inlineStr">
@@ -23286,7 +23350,11 @@
           <t>披头士乐队&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C717" s="1" t="inlineStr"/>
+      <c r="C717" s="1" t="inlineStr">
+        <is>
+          <t>/beˈatle/</t>
+        </is>
+      </c>
       <c r="D717" s="1" t="inlineStr">
         <is>
           <t>披头士乐队</t>
@@ -23407,7 +23475,7 @@
       </c>
       <c r="B721" s="1" t="inlineStr">
         <is>
-          <t>[eɡstɾaˈeɾ] 提取物&lt;动&gt;</t>
+          <t>[/eɡstɾaˈeɾ/] 提取；拔出；开采&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C721" s="1" t="inlineStr">
@@ -23417,7 +23485,7 @@
       </c>
       <c r="D721" s="1" t="inlineStr">
         <is>
-          <t>提取物</t>
+          <t>提取；拔出；开采</t>
         </is>
       </c>
       <c r="E721" s="1" t="inlineStr">
@@ -23535,7 +23603,7 @@
       </c>
       <c r="B725" s="1" t="inlineStr">
         <is>
-          <t>[dipuˈtado] 副手&lt;名&gt;</t>
+          <t>[/dipuˈtado/] 议员；代表&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C725" s="1" t="inlineStr">
@@ -23545,7 +23613,7 @@
       </c>
       <c r="D725" s="1" t="inlineStr">
         <is>
-          <t>副手</t>
+          <t>议员；代表</t>
         </is>
       </c>
       <c r="E725" s="1" t="inlineStr">
@@ -23919,7 +23987,7 @@
       </c>
       <c r="B737" s="1" t="inlineStr">
         <is>
-          <t>[ˈʝaɾda] 院子&lt;名&gt;</t>
+          <t>[/ˈʝaɾda/] 码（长度单位）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C737" s="1" t="inlineStr">
@@ -23929,7 +23997,7 @@
       </c>
       <c r="D737" s="1" t="inlineStr">
         <is>
-          <t>院子</t>
+          <t>码（长度单位）</t>
         </is>
       </c>
       <c r="E737" s="1" t="inlineStr">
@@ -24335,7 +24403,7 @@
       </c>
       <c r="B750" s="1" t="inlineStr">
         <is>
-          <t>[ˈmaɾa] 玛丽亚&lt;名&gt;</t>
+          <t>[/ˈmaɾa/] 长耳豚鼠；帮派&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C750" s="1" t="inlineStr">
@@ -24345,7 +24413,7 @@
       </c>
       <c r="D750" s="1" t="inlineStr">
         <is>
-          <t>玛丽亚</t>
+          <t>长耳豚鼠；帮派</t>
         </is>
       </c>
       <c r="E750" s="1" t="inlineStr">
@@ -24495,7 +24563,7 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>[aˈɡɾado] 请&lt;名&gt;</t>
+          <t>[/aˈɡɾado/] 喜好；愉快；好感&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C755" s="1" t="inlineStr">
@@ -24505,7 +24573,7 @@
       </c>
       <c r="D755" s="1" t="inlineStr">
         <is>
-          <t>请</t>
+          <t>喜好；愉快；好感</t>
         </is>
       </c>
       <c r="E755" s="1" t="inlineStr">
@@ -24527,7 +24595,7 @@
       </c>
       <c r="B756" s="1" t="inlineStr">
         <is>
-          <t>[ˈpont͡ʃe] 冲孔&lt;名&gt;</t>
+          <t>[/ˈpont͡ʃe/] 潘趣酒；宾治酒&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C756" s="1" t="inlineStr">
@@ -24537,7 +24605,7 @@
       </c>
       <c r="D756" s="1" t="inlineStr">
         <is>
-          <t>冲孔</t>
+          <t>潘趣酒；宾治酒</t>
         </is>
       </c>
       <c r="E756" s="1" t="inlineStr">
@@ -24719,7 +24787,7 @@
       </c>
       <c r="B762" s="1" t="inlineStr">
         <is>
-          <t>[desmaˈʝaɾ] 微弱的&lt;动&gt;</t>
+          <t>[desmaˈʝaɾ] 昏倒；使昏厥&lt;动&gt;</t>
         </is>
       </c>
       <c r="C762" s="1" t="inlineStr">
@@ -24729,7 +24797,7 @@
       </c>
       <c r="D762" s="1" t="inlineStr">
         <is>
-          <t>微弱的</t>
+          <t>昏倒；使昏厥</t>
         </is>
       </c>
       <c r="E762" s="1" t="inlineStr">
@@ -24921,7 +24989,7 @@
       </c>
       <c r="D768" s="1" t="inlineStr">
         <is>
-          <t>冒犯</t>
+          <t>冒犯&lt;名&gt;（正确拼写为 ofensa）</t>
         </is>
       </c>
       <c r="E768" s="1" t="inlineStr">
@@ -25138,10 +25206,14 @@
           <t>特雷&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C775" s="1" t="inlineStr"/>
+      <c r="C775" s="1" t="inlineStr">
+        <is>
+          <t>/tɾˈej/</t>
+        </is>
+      </c>
       <c r="D775" s="1" t="inlineStr">
         <is>
-          <t>特雷</t>
+          <t>非西班牙语词汇，应删除</t>
         </is>
       </c>
       <c r="E775" s="1" t="inlineStr">
@@ -25227,7 +25299,7 @@
       </c>
       <c r="B778" s="1" t="inlineStr">
         <is>
-          <t>[ˈbito] 维托&lt;名&gt;</t>
+          <t>[/ˈbito/] 维托舞（西班牙一种舞蹈）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C778" s="1" t="inlineStr">
@@ -25237,7 +25309,7 @@
       </c>
       <c r="D778" s="1" t="inlineStr">
         <is>
-          <t>维托</t>
+          <t>维托舞（西班牙一种舞蹈）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E778" s="1" t="inlineStr">
@@ -25326,7 +25398,11 @@
           <t>巴&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C781" s="1" t="inlineStr"/>
+      <c r="C781" s="1" t="inlineStr">
+        <is>
+          <t>/bˈa/</t>
+        </is>
+      </c>
       <c r="D781" s="1" t="inlineStr">
         <is>
           <t>巴</t>
@@ -25383,7 +25459,7 @@
       </c>
       <c r="B783" s="1" t="inlineStr">
         <is>
-          <t>[aplasˈtaɾ] 暗恋&lt;动&gt;</t>
+          <t>[aplasˈtaɾ] 压碎；压扁；粉碎&lt;动&gt;</t>
         </is>
       </c>
       <c r="C783" s="1" t="inlineStr">
@@ -25393,7 +25469,7 @@
       </c>
       <c r="D783" s="1" t="inlineStr">
         <is>
-          <t>暗恋</t>
+          <t>压碎；压扁；粉碎</t>
         </is>
       </c>
       <c r="E783" s="1" t="inlineStr">
@@ -25415,7 +25491,7 @@
       </c>
       <c r="B784" s="1" t="inlineStr">
         <is>
-          <t>[auˈdaθ] 粗体&lt;形&gt;</t>
+          <t>[auˈdaθ] 大胆的；勇敢的；鲁莽的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C784" s="1" t="inlineStr">
@@ -25425,7 +25501,7 @@
       </c>
       <c r="D784" s="1" t="inlineStr">
         <is>
-          <t>粗体</t>
+          <t>大胆的；勇敢的；鲁莽的</t>
         </is>
       </c>
       <c r="E784" s="1" t="inlineStr">
@@ -25511,7 +25587,7 @@
       </c>
       <c r="B787" s="1" t="inlineStr">
         <is>
-          <t>[aniˈmado] 动画&lt;形&gt;</t>
+          <t>[aniˈmado] 热闹的；活跃的；生气勃勃的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C787" s="1" t="inlineStr">
@@ -25521,7 +25597,7 @@
       </c>
       <c r="D787" s="1" t="inlineStr">
         <is>
-          <t>动画</t>
+          <t>热闹的；活跃的；生气勃勃的</t>
         </is>
       </c>
       <c r="E787" s="1" t="inlineStr">
@@ -26023,7 +26099,7 @@
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>[roˈʝal] 皇家的&lt;名&gt;</t>
+          <t>[/roˈʝal/] 皇家的（西语应为 real）&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C803" s="1" t="inlineStr">
@@ -26033,7 +26109,7 @@
       </c>
       <c r="D803" s="1" t="inlineStr">
         <is>
-          <t>皇家的</t>
+          <t>皇家的（西语应为 real）&lt;形&gt;</t>
         </is>
       </c>
       <c r="E803" s="1" t="inlineStr">
@@ -26119,7 +26195,7 @@
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
-          <t>[reˈɡaθo] 圈&lt;名&gt;</t>
+          <t>[reˈɡaθo] 膝上；怀&lt;名&gt;</t>
         </is>
       </c>
       <c r="C806" s="1" t="inlineStr">
@@ -26129,7 +26205,7 @@
       </c>
       <c r="D806" s="1" t="inlineStr">
         <is>
-          <t>圈</t>
+          <t>膝上；怀</t>
         </is>
       </c>
       <c r="E806" s="1" t="inlineStr">
@@ -26279,7 +26355,7 @@
       </c>
       <c r="B811" s="1" t="inlineStr">
         <is>
-          <t>[ˈfi] 菲&lt;名&gt;</t>
+          <t>[/ˈfi/] 呸；表示厌恶或拒绝的感叹声&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C811" s="1" t="inlineStr">
@@ -26289,7 +26365,7 @@
       </c>
       <c r="D811" s="1" t="inlineStr">
         <is>
-          <t>菲</t>
+          <t>呸；表示厌恶或拒绝的感叹声</t>
         </is>
       </c>
       <c r="E811" s="1" t="inlineStr">
@@ -26311,7 +26387,7 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>[inteˈɾese] 兴趣&lt;名&gt;</t>
+          <t>[/inteˈɾese/] interesar 的虚拟式（他/她/您使感兴趣）&lt;动&gt;；名词应为 interés（兴趣）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C812" s="1" t="inlineStr">
@@ -26321,7 +26397,7 @@
       </c>
       <c r="D812" s="1" t="inlineStr">
         <is>
-          <t>兴趣</t>
+          <t>interesar 的虚拟式（他/她/您使感兴趣）&lt;动&gt;；名词应为 interés（兴趣）</t>
         </is>
       </c>
       <c r="E812" s="1" t="inlineStr">
@@ -26343,7 +26419,7 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>[motibaˈθjon] 动机&lt;名&gt;</t>
+          <t>[/motibaˈθjon/] 动力；激励；动机说明&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C813" s="1" t="inlineStr">
@@ -26353,7 +26429,7 @@
       </c>
       <c r="D813" s="1" t="inlineStr">
         <is>
-          <t>动机</t>
+          <t>动力；激励；动机说明&lt;名&gt;</t>
         </is>
       </c>
       <c r="E813" s="1" t="inlineStr">
@@ -26407,7 +26483,7 @@
       </c>
       <c r="B815" s="1" t="inlineStr">
         <is>
-          <t>[batiˈkano] 梵蒂冈&lt;名&gt;</t>
+          <t>[/batiˈkano/] 梵蒂冈的；罗马教廷的&lt;形&gt;（el Vaticano 才指梵蒂冈&lt;名&gt;）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C815" s="1" t="inlineStr">
@@ -26417,7 +26493,7 @@
       </c>
       <c r="D815" s="1" t="inlineStr">
         <is>
-          <t>梵蒂冈</t>
+          <t>梵蒂冈的；罗马教廷的&lt;形&gt;（el Vaticano 才指梵蒂冈&lt;名&gt;）</t>
         </is>
       </c>
       <c r="E815" s="1" t="inlineStr">
@@ -26503,7 +26579,7 @@
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>[akaˈbada] 完成&lt;名&gt;</t>
+          <t>[/akaˈbada/] 结束；结局&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C818" s="1" t="inlineStr">
@@ -26513,7 +26589,7 @@
       </c>
       <c r="D818" s="1" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>结束；结局&lt;名&gt;</t>
         </is>
       </c>
       <c r="E818" s="1" t="inlineStr">
@@ -26791,7 +26867,7 @@
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
-          <t>[kaˈreta] 购物车&lt;名&gt;</t>
+          <t>[kaˈreta] 牛车；大车&lt;名&gt;</t>
         </is>
       </c>
       <c r="C827" s="1" t="inlineStr">
@@ -26801,7 +26877,7 @@
       </c>
       <c r="D827" s="1" t="inlineStr">
         <is>
-          <t>购物车</t>
+          <t>牛车；大车</t>
         </is>
       </c>
       <c r="E827" s="1" t="inlineStr">
@@ -27079,7 +27155,7 @@
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>[entɾaˈbaɾ] 输入&lt;动&gt;</t>
+          <t>[entɾaˈbaɾ] 阻碍；阻塞；使停滞&lt;动&gt;</t>
         </is>
       </c>
       <c r="C836" s="1" t="inlineStr">
@@ -27089,7 +27165,7 @@
       </c>
       <c r="D836" s="1" t="inlineStr">
         <is>
-          <t>输入</t>
+          <t>阻碍；阻塞；使停滞</t>
         </is>
       </c>
       <c r="E836" s="1" t="inlineStr">
@@ -27111,7 +27187,7 @@
       </c>
       <c r="B837" s="1" t="inlineStr">
         <is>
-          <t>[mediˈkaɾ] 吃药&lt;动&gt;</t>
+          <t>[/mediˈkaɾ/] 医治；给…用药&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C837" s="1" t="inlineStr">
@@ -27121,7 +27197,7 @@
       </c>
       <c r="D837" s="1" t="inlineStr">
         <is>
-          <t>吃药</t>
+          <t>医治；给…用药&lt;动&gt;</t>
         </is>
       </c>
       <c r="E837" s="1" t="inlineStr">
@@ -27239,7 +27315,7 @@
       </c>
       <c r="B841" s="1" t="inlineStr">
         <is>
-          <t>[bɾeˈaɾ] 焦油&lt;动&gt;</t>
+          <t>[bɾeˈaɾ] 涂焦油；使劳累；痛打&lt;动&gt;</t>
         </is>
       </c>
       <c r="C841" s="1" t="inlineStr">
@@ -27249,7 +27325,7 @@
       </c>
       <c r="D841" s="1" t="inlineStr">
         <is>
-          <t>焦油</t>
+          <t>涂焦油；使劳累；痛打</t>
         </is>
       </c>
       <c r="E841" s="1" t="inlineStr">
@@ -27367,13 +27443,17 @@
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
-          <t>町&lt;叹&gt;</t>
-        </is>
-      </c>
-      <c r="C845" s="1" t="inlineStr"/>
+          <t>唤鸡声；唤鸡的呼声&lt;叹&gt;</t>
+        </is>
+      </c>
+      <c r="C845" s="1" t="inlineStr">
+        <is>
+          <t>/tʃˈo/</t>
+        </is>
+      </c>
       <c r="D845" s="1" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>唤鸡声；唤鸡的呼声</t>
         </is>
       </c>
       <c r="E845" s="1" t="inlineStr">
@@ -27430,7 +27510,11 @@
           <t>荷兰&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C847" s="1" t="inlineStr"/>
+      <c r="C847" s="1" t="inlineStr">
+        <is>
+          <t>/olanda/</t>
+        </is>
+      </c>
       <c r="D847" s="1" t="inlineStr">
         <is>
           <t>荷兰</t>
@@ -27458,7 +27542,11 @@
           <t>非法地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C848" s="1" t="inlineStr"/>
+      <c r="C848" s="1" t="inlineStr">
+        <is>
+          <t>/ileɣalmente/</t>
+        </is>
+      </c>
       <c r="D848" s="1" t="inlineStr">
         <is>
           <t>非法地</t>
@@ -27867,7 +27955,7 @@
       </c>
       <c r="B861" s="1" t="inlineStr">
         <is>
-          <t>[tenˈdido] 说谎&lt;名&gt;</t>
+          <t>[tenˈdido] 铺设；伸展；躺卧；看台；观众&lt;名&gt;</t>
         </is>
       </c>
       <c r="C861" s="1" t="inlineStr">
@@ -27877,7 +27965,7 @@
       </c>
       <c r="D861" s="1" t="inlineStr">
         <is>
-          <t>说谎</t>
+          <t>铺设；伸展；躺卧；看台；观众</t>
         </is>
       </c>
       <c r="E861" s="1" t="inlineStr">
@@ -27902,7 +27990,11 @@
           <t>撒旦&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C862" s="1" t="inlineStr"/>
+      <c r="C862" s="1" t="inlineStr">
+        <is>
+          <t>/saˈtan/</t>
+        </is>
+      </c>
       <c r="D862" s="1" t="inlineStr">
         <is>
           <t>撒旦</t>
@@ -28087,7 +28179,7 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>[kompoɾˈtaɾ] 表现&lt;动&gt;</t>
+          <t>[/kompoɾˈtaɾ/] 意味着；包含（comportarse 才是“表现”）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C868" s="1" t="inlineStr">
@@ -28097,7 +28189,7 @@
       </c>
       <c r="D868" s="1" t="inlineStr">
         <is>
-          <t>表现</t>
+          <t>意味着；包含（comportarse 才是“表现”）</t>
         </is>
       </c>
       <c r="E868" s="1" t="inlineStr">
@@ -28183,13 +28275,17 @@
       </c>
       <c r="B871" s="1" t="inlineStr">
         <is>
-          <t>托克&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C871" s="1" t="inlineStr"/>
+          <t>嗒；敲击声&lt;名&gt;</t>
+        </is>
+      </c>
+      <c r="C871" s="1" t="inlineStr">
+        <is>
+          <t>/tˈaθ/</t>
+        </is>
+      </c>
       <c r="D871" s="1" t="inlineStr">
         <is>
-          <t>托克</t>
+          <t>嗒；敲击声</t>
         </is>
       </c>
       <c r="E871" s="1" t="inlineStr">
@@ -28243,7 +28339,7 @@
       </c>
       <c r="B873" s="1" t="inlineStr">
         <is>
-          <t>[emˈpate] 领带&lt;名&gt;</t>
+          <t>[emˈpate] 平局；平手&lt;名&gt;</t>
         </is>
       </c>
       <c r="C873" s="1" t="inlineStr">
@@ -28253,7 +28349,7 @@
       </c>
       <c r="D873" s="1" t="inlineStr">
         <is>
-          <t>领带</t>
+          <t>平局；平手</t>
         </is>
       </c>
       <c r="E873" s="1" t="inlineStr">
@@ -28979,7 +29075,7 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>[ˌɡɾabeˈmente] 认真地&lt;副&gt;</t>
+          <t>[ˌɡɾabeˈmente] 严重地；沉重地&lt;副&gt;</t>
         </is>
       </c>
       <c r="C896" s="1" t="inlineStr">
@@ -28989,7 +29085,7 @@
       </c>
       <c r="D896" s="1" t="inlineStr">
         <is>
-          <t>认真地</t>
+          <t>严重地；沉重地</t>
         </is>
       </c>
       <c r="E896" s="1" t="inlineStr">
@@ -29043,13 +29139,17 @@
       </c>
       <c r="B898" s="1" t="inlineStr">
         <is>
-          <t>我提出&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C898" s="1" t="inlineStr"/>
+          <t>我抚养；我养育&lt;动&gt;</t>
+        </is>
+      </c>
+      <c r="C898" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkɾje/</t>
+        </is>
+      </c>
       <c r="D898" s="1" t="inlineStr">
         <is>
-          <t>我提出</t>
+          <t>我抚养；我养育</t>
         </is>
       </c>
       <c r="E898" s="1" t="inlineStr">
@@ -29071,7 +29171,7 @@
       </c>
       <c r="B899" s="1" t="inlineStr">
         <is>
-          <t>[rekuˈriɾ] 度假村&lt;动&gt;</t>
+          <t>[/rekuˈriɾ/] 求助；诉诸；采用&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C899" s="1" t="inlineStr">
@@ -29081,7 +29181,7 @@
       </c>
       <c r="D899" s="1" t="inlineStr">
         <is>
-          <t>度假村</t>
+          <t>求助；诉诸；采用</t>
         </is>
       </c>
       <c r="E899" s="1" t="inlineStr">
@@ -29391,7 +29491,7 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>[teɾˈneɾa] 牛肉&lt;名&gt;</t>
+          <t>[/teɾˈneɾa/] 小牛肉&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C909" s="1" t="inlineStr">
@@ -29401,7 +29501,7 @@
       </c>
       <c r="D909" s="1" t="inlineStr">
         <is>
-          <t>牛肉</t>
+          <t>小牛肉&lt;名&gt;</t>
         </is>
       </c>
       <c r="E909" s="1" t="inlineStr">
@@ -29679,7 +29779,7 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>[peˈon] 典当&lt;名&gt;</t>
+          <t>[/peˈon/] 雇工；苦力；（国际象棋的）兵&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C918" s="1" t="inlineStr">
@@ -29689,7 +29789,7 @@
       </c>
       <c r="D918" s="1" t="inlineStr">
         <is>
-          <t>典当</t>
+          <t>雇工；苦力；（国际象棋的）兵</t>
         </is>
       </c>
       <c r="E918" s="1" t="inlineStr">
@@ -29775,7 +29875,7 @@
       </c>
       <c r="B921" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃupa] 糟透了&lt;名&gt;</t>
+          <t>[/ˈt͡ʃupa/] 吮吸；皮夹克&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C921" s="1" t="inlineStr">
@@ -29785,7 +29885,7 @@
       </c>
       <c r="D921" s="1" t="inlineStr">
         <is>
-          <t>糟透了</t>
+          <t>吮吸；皮夹克</t>
         </is>
       </c>
       <c r="E921" s="1" t="inlineStr">
@@ -30127,7 +30227,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>[ˈfjaɾ] 合法的&lt;动&gt;</t>
+          <t>[/ˈfjaɾ/] 信任；赊账；赊卖&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C932" s="1" t="inlineStr">
@@ -30137,7 +30237,7 @@
       </c>
       <c r="D932" s="1" t="inlineStr">
         <is>
-          <t>合法的</t>
+          <t>信任；赊账；赊卖</t>
         </is>
       </c>
       <c r="E932" s="1" t="inlineStr">
@@ -30255,7 +30355,7 @@
       </c>
       <c r="B936" s="1" t="inlineStr">
         <is>
-          <t>[ˈsumo] 相扑&lt;名&gt;</t>
+          <t>[/ˈsumo/] 最高的；至高无上的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C936" s="1" t="inlineStr">
@@ -30265,7 +30365,7 @@
       </c>
       <c r="D936" s="1" t="inlineStr">
         <is>
-          <t>相扑</t>
+          <t>最高的；至高无上的</t>
         </is>
       </c>
       <c r="E936" s="1" t="inlineStr">
@@ -30415,7 +30515,7 @@
       </c>
       <c r="B941" s="1" t="inlineStr">
         <is>
-          <t>[pɾesenˈtiɾ] 现在&lt;动&gt;</t>
+          <t>[/pɾesenˈtiɾ/] 预感；预知&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C941" s="1" t="inlineStr">
@@ -30425,7 +30525,7 @@
       </c>
       <c r="D941" s="1" t="inlineStr">
         <is>
-          <t>现在</t>
+          <t>预感；预知</t>
         </is>
       </c>
       <c r="E941" s="1" t="inlineStr">
@@ -30479,7 +30579,7 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>[auˈɾoɾa] 极光&lt;名&gt;</t>
+          <t>[/auˈɾoɾa/] 黎明；曙光&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C943" s="1" t="inlineStr">
@@ -30489,7 +30589,7 @@
       </c>
       <c r="D943" s="1" t="inlineStr">
         <is>
-          <t>极光</t>
+          <t>黎明；曙光&lt;名&gt;</t>
         </is>
       </c>
       <c r="E943" s="1" t="inlineStr">
@@ -30575,7 +30675,7 @@
       </c>
       <c r="B946" s="1" t="inlineStr">
         <is>
-          <t>[sanˈɡineo] 血&lt;形&gt;</t>
+          <t>[/sanˈɡineo/] 血液的；多血质的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C946" s="1" t="inlineStr">
@@ -30585,7 +30685,7 @@
       </c>
       <c r="D946" s="1" t="inlineStr">
         <is>
-          <t>血</t>
+          <t>血液的；多血质的</t>
         </is>
       </c>
       <c r="E946" s="1" t="inlineStr">
@@ -30607,7 +30707,7 @@
       </c>
       <c r="B947" s="1" t="inlineStr">
         <is>
-          <t>[reaˈleθa] 版税&lt;名&gt;</t>
+          <t>[/reaˈleθa/] 王室；王族&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C947" s="1" t="inlineStr">
@@ -30617,7 +30717,7 @@
       </c>
       <c r="D947" s="1" t="inlineStr">
         <is>
-          <t>版税</t>
+          <t>王室；王族</t>
         </is>
       </c>
       <c r="E947" s="1" t="inlineStr">
@@ -31119,7 +31219,7 @@
       </c>
       <c r="B963" s="1" t="inlineStr">
         <is>
-          <t>[eskoˈtiʝa] 孵化&lt;名&gt;</t>
+          <t>[/eskoˈtiʝa/] 舱口；舱口盖&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C963" s="1" t="inlineStr">
@@ -31129,7 +31229,7 @@
       </c>
       <c r="D963" s="1" t="inlineStr">
         <is>
-          <t>孵化</t>
+          <t>舱口；舱口盖</t>
         </is>
       </c>
       <c r="E963" s="1" t="inlineStr">
@@ -31314,7 +31414,11 @@
           <t>平安夜&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C969" s="1" t="inlineStr"/>
+      <c r="C969" s="1" t="inlineStr">
+        <is>
+          <t>/notʃebuˈena/</t>
+        </is>
+      </c>
       <c r="D969" s="1" t="inlineStr">
         <is>
           <t>平安夜</t>
@@ -31403,7 +31507,7 @@
       </c>
       <c r="B972" s="1" t="inlineStr">
         <is>
-          <t>[pelukeˈɾia] 理发师&lt;名&gt;</t>
+          <t>[/pelukeˈɾia/] 理发店；理发业&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C972" s="1" t="inlineStr">
@@ -31413,7 +31517,7 @@
       </c>
       <c r="D972" s="1" t="inlineStr">
         <is>
-          <t>理发师</t>
+          <t>理发店；理发业</t>
         </is>
       </c>
       <c r="E972" s="1" t="inlineStr">
@@ -31694,7 +31798,11 @@
           <t>武士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C981" s="1" t="inlineStr"/>
+      <c r="C981" s="1" t="inlineStr">
+        <is>
+          <t>/samaˈɾaj/</t>
+        </is>
+      </c>
       <c r="D981" s="1" t="inlineStr">
         <is>
           <t>武士</t>
@@ -32071,7 +32179,7 @@
       </c>
       <c r="B993" s="1" t="inlineStr">
         <is>
-          <t>[ˈlait] 光&lt;形&gt;</t>
+          <t>[/ˈlait/] 低热量的；轻型的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C993" s="1" t="inlineStr">
@@ -32081,7 +32189,7 @@
       </c>
       <c r="D993" s="1" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>低热量的；轻型的</t>
         </is>
       </c>
       <c r="E993" s="1" t="inlineStr">
@@ -32295,7 +32403,7 @@
       </c>
       <c r="B1000" s="1" t="inlineStr">
         <is>
-          <t>[kommobeˈdoɾ] 移动&lt;形&gt;</t>
+          <t>[/kommobeˈdoɾ/] 感人的；动人的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1000" s="1" t="inlineStr">
@@ -32305,7 +32413,7 @@
       </c>
       <c r="D1000" s="1" t="inlineStr">
         <is>
-          <t>移动</t>
+          <t>感人的；动人的</t>
         </is>
       </c>
       <c r="E1000" s="1" t="inlineStr">
@@ -32615,7 +32723,7 @@
       </c>
       <c r="B1010" s="1" t="inlineStr">
         <is>
-          <t>[deˈθeno] 十&lt;形&gt;</t>
+          <t>[/deˈθeno/] décimo 第十的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1010" s="1" t="inlineStr">
@@ -32625,7 +32733,7 @@
       </c>
       <c r="D1010" s="1" t="inlineStr">
         <is>
-          <t>十</t>
+          <t>décimo 第十的</t>
         </is>
       </c>
       <c r="E1010" s="1" t="inlineStr">
@@ -32903,7 +33011,7 @@
       </c>
       <c r="B1019" s="1" t="inlineStr">
         <is>
-          <t>[diˈlema] 困境&lt;名&gt;</t>
+          <t>[/diˈlema/] 两难；进退两难&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1019" s="1" t="inlineStr">
@@ -32913,7 +33021,7 @@
       </c>
       <c r="D1019" s="1" t="inlineStr">
         <is>
-          <t>困境</t>
+          <t>两难；进退两难&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1019" s="1" t="inlineStr">
@@ -32935,7 +33043,7 @@
       </c>
       <c r="B1020" s="1" t="inlineStr">
         <is>
-          <t>[liˈbɾaɾ] 免费&lt;动&gt;</t>
+          <t>[/liˈbɾaɾ/] 解放；使摆脱；进行（战斗）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1020" s="1" t="inlineStr">
@@ -32945,7 +33053,7 @@
       </c>
       <c r="D1020" s="1" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>解放；使摆脱；进行（战斗）</t>
         </is>
       </c>
       <c r="E1020" s="1" t="inlineStr">
@@ -33319,7 +33427,7 @@
       </c>
       <c r="B1032" s="1" t="inlineStr">
         <is>
-          <t>[komˈpadɾe] 同伴&lt;名&gt;</t>
+          <t>[/komˈpadɾe/] 教父；密友&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1032" s="1" t="inlineStr">
@@ -33329,7 +33437,7 @@
       </c>
       <c r="D1032" s="1" t="inlineStr">
         <is>
-          <t>同伴</t>
+          <t>教父；密友&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1032" s="1" t="inlineStr">
@@ -33834,7 +33942,11 @@
           <t>恶习&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1048" s="1" t="inlineStr"/>
+      <c r="C1048" s="1" t="inlineStr">
+        <is>
+          <t>/ˈbiθe/</t>
+        </is>
+      </c>
       <c r="D1048" s="1" t="inlineStr">
         <is>
           <t>恶习</t>
@@ -34147,7 +34259,7 @@
       </c>
       <c r="B1058" s="1" t="inlineStr">
         <is>
-          <t>[ˈraix] 帝国&lt;名&gt;</t>
+          <t>[/ˈraix/] 帝国；德意志帝国&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1058" s="1" t="inlineStr">
@@ -34157,7 +34269,7 @@
       </c>
       <c r="D1058" s="1" t="inlineStr">
         <is>
-          <t>帝国</t>
+          <t>帝国；德意志帝国</t>
         </is>
       </c>
       <c r="E1058" s="1" t="inlineStr">
@@ -34435,7 +34547,7 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>[ɡolˈpeo] 击中&lt;名&gt;</t>
+          <t>[/ɡolˈpeo/] 敲击；叩击&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1067" s="1" t="inlineStr">
@@ -34445,7 +34557,7 @@
       </c>
       <c r="D1067" s="1" t="inlineStr">
         <is>
-          <t>击中</t>
+          <t>敲击；叩击&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1067" s="1" t="inlineStr">
@@ -34467,7 +34579,7 @@
       </c>
       <c r="B1068" s="1" t="inlineStr">
         <is>
-          <t>[adobˈtado] 通过&lt;名&gt;</t>
+          <t>[/adobˈtado/] 被收养的；养子&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1068" s="1" t="inlineStr">
@@ -34477,7 +34589,7 @@
       </c>
       <c r="D1068" s="1" t="inlineStr">
         <is>
-          <t>通过</t>
+          <t>被收养的；养子</t>
         </is>
       </c>
       <c r="E1068" s="1" t="inlineStr">
@@ -35139,7 +35251,7 @@
       </c>
       <c r="B1089" s="1" t="inlineStr">
         <is>
-          <t>[ˈliθa] 丽莎&lt;名&gt;</t>
+          <t>[/ˈliθa/] 战斗；搏斗；竞赛&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1089" s="1" t="inlineStr">
@@ -35149,7 +35261,7 @@
       </c>
       <c r="D1089" s="1" t="inlineStr">
         <is>
-          <t>丽莎</t>
+          <t>战斗；搏斗；竞赛</t>
         </is>
       </c>
       <c r="E1089" s="1" t="inlineStr">
@@ -35683,7 +35795,7 @@
       </c>
       <c r="B1106" s="1" t="inlineStr">
         <is>
-          <t>[ˈflwiɾ] 流量&lt;动&gt;</t>
+          <t>[/ˈflwiɾ/] 流动；流出&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1106" s="1" t="inlineStr">
@@ -35693,7 +35805,7 @@
       </c>
       <c r="D1106" s="1" t="inlineStr">
         <is>
-          <t>流量</t>
+          <t>流动；流出</t>
         </is>
       </c>
       <c r="E1106" s="1" t="inlineStr">
@@ -35715,7 +35827,7 @@
       </c>
       <c r="B1107" s="1" t="inlineStr">
         <is>
-          <t>[maˈdɾiθa] 马德里斯&lt;名&gt;</t>
+          <t>[/maˈdɾiθa/] 继母&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1107" s="1" t="inlineStr">
@@ -35725,7 +35837,7 @@
       </c>
       <c r="D1107" s="1" t="inlineStr">
         <is>
-          <t>马德里斯</t>
+          <t>继母</t>
         </is>
       </c>
       <c r="E1107" s="1" t="inlineStr">
@@ -35843,7 +35955,7 @@
       </c>
       <c r="B1111" s="1" t="inlineStr">
         <is>
-          <t>[tenˈdeɾ] 倾向于&lt;动&gt;</t>
+          <t>[/tenˈdeɾ/] 铺开，晾晒&lt;动&gt;；tender a 倾向于&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1111" s="1" t="inlineStr">
@@ -35853,7 +35965,7 @@
       </c>
       <c r="D1111" s="1" t="inlineStr">
         <is>
-          <t>倾向于</t>
+          <t>铺开，晾晒&lt;动&gt;；tender a 倾向于&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1111" s="1" t="inlineStr">
@@ -35939,7 +36051,7 @@
       </c>
       <c r="B1114" s="1" t="inlineStr">
         <is>
-          <t>[enˈtɾante] 传入&lt;形&gt;</t>
+          <t>[/enˈtɾante/] 即将到来的；开胃菜&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1114" s="1" t="inlineStr">
@@ -35949,7 +36061,7 @@
       </c>
       <c r="D1114" s="1" t="inlineStr">
         <is>
-          <t>传入</t>
+          <t>即将到来的；开胃菜</t>
         </is>
       </c>
       <c r="E1114" s="1" t="inlineStr">
@@ -35974,7 +36086,11 @@
           <t>按摩浴缸&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1115" s="1" t="inlineStr"/>
+      <c r="C1115" s="1" t="inlineStr">
+        <is>
+          <t>/xakˈuθθi/</t>
+        </is>
+      </c>
       <c r="D1115" s="1" t="inlineStr">
         <is>
           <t>按摩浴缸</t>
@@ -36095,7 +36211,7 @@
       </c>
       <c r="B1119" s="1" t="inlineStr">
         <is>
-          <t>[koˈrido] 跑&lt;名&gt;</t>
+          <t>[/koˈrido/] 墨西哥民歌；奔跑的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1119" s="1" t="inlineStr">
@@ -36105,7 +36221,7 @@
       </c>
       <c r="D1119" s="1" t="inlineStr">
         <is>
-          <t>跑</t>
+          <t>墨西哥民歌；奔跑的</t>
         </is>
       </c>
       <c r="E1119" s="1" t="inlineStr">
@@ -36223,7 +36339,7 @@
       </c>
       <c r="B1123" s="1" t="inlineStr">
         <is>
-          <t>[maɾˈkesa] 榄尖形&lt;名&gt;</t>
+          <t>[/maɾˈkesa/] 侯爵夫人；女侯爵&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1123" s="1" t="inlineStr">
@@ -36233,7 +36349,7 @@
       </c>
       <c r="D1123" s="1" t="inlineStr">
         <is>
-          <t>榄尖形</t>
+          <t>侯爵夫人；女侯爵</t>
         </is>
       </c>
       <c r="E1123" s="1" t="inlineStr">
@@ -36260,7 +36376,7 @@
       </c>
       <c r="C1124" s="1" t="inlineStr">
         <is>
-          <t>/etˈθeteɾa/ [et̪ˈθe.t̪e.ɾa]</t>
+          <t>/etˈθeteɾa/</t>
         </is>
       </c>
       <c r="D1124" s="1" t="inlineStr">
@@ -36319,7 +36435,7 @@
       </c>
       <c r="B1126" s="1" t="inlineStr">
         <is>
-          <t>[ˈsikiko] 通灵的&lt;形&gt;</t>
+          <t>[/ˈsikiko/] 精神的，心理的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1126" s="1" t="inlineStr">
@@ -36329,7 +36445,7 @@
       </c>
       <c r="D1126" s="1" t="inlineStr">
         <is>
-          <t>通灵的</t>
+          <t>精神的，心理的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1126" s="1" t="inlineStr">
@@ -36511,7 +36627,7 @@
       </c>
       <c r="B1132" s="1" t="inlineStr">
         <is>
-          <t>[unˈdiɾ] 水槽&lt;动&gt;</t>
+          <t>[/unˈdiɾ/] 使沉没；使下沉；使陷入&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1132" s="1" t="inlineStr">
@@ -36521,7 +36637,7 @@
       </c>
       <c r="D1132" s="1" t="inlineStr">
         <is>
-          <t>水槽</t>
+          <t>使沉没；使下沉；使陷入</t>
         </is>
       </c>
       <c r="E1132" s="1" t="inlineStr">
@@ -36543,7 +36659,7 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>[desmaˈʝado] 晕倒了&lt;形&gt;</t>
+          <t>[/desmaˈʝado/] 昏倒的，晕厥的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1133" s="1" t="inlineStr">
@@ -36553,7 +36669,7 @@
       </c>
       <c r="D1133" s="1" t="inlineStr">
         <is>
-          <t>晕倒了</t>
+          <t>昏倒的，晕厥的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1133" s="1" t="inlineStr">
@@ -36735,7 +36851,7 @@
       </c>
       <c r="B1139" s="1" t="inlineStr">
         <is>
-          <t>[ˈtik] 勾选&lt;名&gt;</t>
+          <t>[/ˈtik/] 抽搐；痉挛；习惯性动作&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1139" s="1" t="inlineStr">
@@ -36745,7 +36861,7 @@
       </c>
       <c r="D1139" s="1" t="inlineStr">
         <is>
-          <t>勾选</t>
+          <t>抽搐；痉挛；习惯性动作</t>
         </is>
       </c>
       <c r="E1139" s="1" t="inlineStr">
@@ -36831,7 +36947,7 @@
       </c>
       <c r="B1142" s="1" t="inlineStr">
         <is>
-          <t>[ˈxake] 检查&lt;名&gt;</t>
+          <t>[/ˈxake/] 将军；威胁&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1142" s="1" t="inlineStr">
@@ -36841,7 +36957,7 @@
       </c>
       <c r="D1142" s="1" t="inlineStr">
         <is>
-          <t>检查</t>
+          <t>将军；威胁</t>
         </is>
       </c>
       <c r="E1142" s="1" t="inlineStr">
@@ -37087,7 +37203,7 @@
       </c>
       <c r="B1150" s="1" t="inlineStr">
         <is>
-          <t>[ˈxama] 贾马&lt;名&gt;</t>
+          <t>[/ˈxama/] 宴会；聚会；狂欢&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1150" s="1" t="inlineStr">
@@ -37097,7 +37213,7 @@
       </c>
       <c r="D1150" s="1" t="inlineStr">
         <is>
-          <t>贾马</t>
+          <t>宴会；聚会；狂欢</t>
         </is>
       </c>
       <c r="E1150" s="1" t="inlineStr">
@@ -37151,7 +37267,7 @@
       </c>
       <c r="B1152" s="1" t="inlineStr">
         <is>
-          <t>[doˈɾaɾ] 棕色&lt;动&gt;</t>
+          <t>[/doˈɾaɾ/] 镀金；使呈金黄色；煎黄&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1152" s="1" t="inlineStr">
@@ -37161,7 +37277,7 @@
       </c>
       <c r="D1152" s="1" t="inlineStr">
         <is>
-          <t>棕色</t>
+          <t>镀金；使呈金黄色；煎黄</t>
         </is>
       </c>
       <c r="E1152" s="1" t="inlineStr">
@@ -37375,7 +37491,7 @@
       </c>
       <c r="B1159" s="1" t="inlineStr">
         <is>
-          <t>[manˈteka] 黄油&lt;名&gt;</t>
+          <t>[/manˈteka/] 猪油；油脂&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1159" s="1" t="inlineStr">
@@ -37385,7 +37501,7 @@
       </c>
       <c r="D1159" s="1" t="inlineStr">
         <is>
-          <t>黄油</t>
+          <t>猪油；油脂&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1159" s="1" t="inlineStr">
@@ -37503,7 +37619,7 @@
       </c>
       <c r="B1163" s="1" t="inlineStr">
         <is>
-          <t>[ˈpoliθa] 政策&lt;名&gt;</t>
+          <t>[/ˈpoliθa/] 保险单；保单&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1163" s="1" t="inlineStr">
@@ -37513,7 +37629,7 @@
       </c>
       <c r="D1163" s="1" t="inlineStr">
         <is>
-          <t>政策</t>
+          <t>保险单；保单</t>
         </is>
       </c>
       <c r="E1163" s="1" t="inlineStr">
@@ -37727,7 +37843,7 @@
       </c>
       <c r="B1170" s="1" t="inlineStr">
         <is>
-          <t>[mateɾniˈdad] 产妇&lt;名&gt;</t>
+          <t>[/mateɾniˈdad/] 母性；母亲身份；产科&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1170" s="1" t="inlineStr">
@@ -37737,7 +37853,7 @@
       </c>
       <c r="D1170" s="1" t="inlineStr">
         <is>
-          <t>产妇</t>
+          <t>母性；母亲身份；产科</t>
         </is>
       </c>
       <c r="E1170" s="1" t="inlineStr">
@@ -37986,7 +38102,11 @@
           <t>出来了&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1178" s="1" t="inlineStr"/>
+      <c r="C1178" s="1" t="inlineStr">
+        <is>
+          <t>/saˈlio/</t>
+        </is>
+      </c>
       <c r="D1178" s="1" t="inlineStr">
         <is>
           <t>出来了</t>
@@ -38459,7 +38579,7 @@
       </c>
       <c r="B1193" s="1" t="inlineStr">
         <is>
-          <t>[tɾiˈbuto] 致敬&lt;名&gt;</t>
+          <t>[/tɾiˈbuto/] 贡品；贡税；致敬&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1193" s="1" t="inlineStr">
@@ -38469,7 +38589,7 @@
       </c>
       <c r="D1193" s="1" t="inlineStr">
         <is>
-          <t>致敬</t>
+          <t>贡品；贡税；致敬</t>
         </is>
       </c>
       <c r="E1193" s="1" t="inlineStr">
@@ -38587,7 +38707,7 @@
       </c>
       <c r="B1197" s="1" t="inlineStr">
         <is>
-          <t>[ˈeis] 王牌&lt;名&gt;</t>
+          <t>[/ˈeis/] 王牌；能手；佼佼者&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1197" s="1" t="inlineStr">
@@ -38597,7 +38717,7 @@
       </c>
       <c r="D1197" s="1" t="inlineStr">
         <is>
-          <t>王牌</t>
+          <t>王牌；能手；佼佼者</t>
         </is>
       </c>
       <c r="E1197" s="1" t="inlineStr">
@@ -38718,7 +38838,11 @@
           <t>奇怪地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1201" s="1" t="inlineStr"/>
+      <c r="C1201" s="1" t="inlineStr">
+        <is>
+          <t>/estɾaˈɲamente/</t>
+        </is>
+      </c>
       <c r="D1201" s="1" t="inlineStr">
         <is>
           <t>奇怪地</t>
@@ -38871,7 +38995,7 @@
       </c>
       <c r="B1206" s="1" t="inlineStr">
         <is>
-          <t>[faˈɾol] 虚张声势&lt;名&gt;</t>
+          <t>[/faˈɾol/] 灯笼；虚张声势&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1206" s="1" t="inlineStr">
@@ -38881,7 +39005,7 @@
       </c>
       <c r="D1206" s="1" t="inlineStr">
         <is>
-          <t>虚张声势</t>
+          <t>灯笼；虚张声势</t>
         </is>
       </c>
       <c r="E1206" s="1" t="inlineStr">
@@ -39063,7 +39187,7 @@
       </c>
       <c r="B1212" s="1" t="inlineStr">
         <is>
-          <t>[ˈkuɾo] 治愈&lt;名&gt;</t>
+          <t>[/ˈkuɾo/] （我）治愈；curar 的第一人称单数现在时&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1212" s="1" t="inlineStr">
@@ -39073,7 +39197,7 @@
       </c>
       <c r="D1212" s="1" t="inlineStr">
         <is>
-          <t>治愈</t>
+          <t>（我）治愈；curar 的第一人称单数现在时</t>
         </is>
       </c>
       <c r="E1212" s="1" t="inlineStr">
@@ -39543,7 +39667,7 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>[buɾˈlaɾ] 模拟&lt;动&gt;</t>
+          <t>[/buɾˈlaɾ/] 嘲弄；愚弄；躲避；规避&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1227" s="1" t="inlineStr">
@@ -39553,7 +39677,7 @@
       </c>
       <c r="D1227" s="1" t="inlineStr">
         <is>
-          <t>模拟</t>
+          <t>嘲弄；愚弄；躲避；规避</t>
         </is>
       </c>
       <c r="E1227" s="1" t="inlineStr">
@@ -39671,7 +39795,7 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>[oɾˈlaɾ] 边界&lt;动&gt;</t>
+          <t>[/oɾˈlaɾ/] 镶边；饰边&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1231" s="1" t="inlineStr">
@@ -39681,7 +39805,7 @@
       </c>
       <c r="D1231" s="1" t="inlineStr">
         <is>
-          <t>边界</t>
+          <t>镶边；饰边</t>
         </is>
       </c>
       <c r="E1231" s="1" t="inlineStr">
@@ -40631,7 +40755,7 @@
       </c>
       <c r="B1261" s="1" t="inlineStr">
         <is>
-          <t>[inkumˈbiɾ] 阻碍&lt;动&gt;</t>
+          <t>[/inkumˈbiɾ/] 是…的职责；归属于&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1261" s="1" t="inlineStr">
@@ -40641,7 +40765,7 @@
       </c>
       <c r="D1261" s="1" t="inlineStr">
         <is>
-          <t>阻碍</t>
+          <t>是…的职责；归属于</t>
         </is>
       </c>
       <c r="E1261" s="1" t="inlineStr">
@@ -40666,7 +40790,11 @@
           <t>锣&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1262" s="1" t="inlineStr"/>
+      <c r="C1262" s="1" t="inlineStr">
+        <is>
+          <t>/ɡoŋ/</t>
+        </is>
+      </c>
       <c r="D1262" s="1" t="inlineStr">
         <is>
           <t>锣</t>
@@ -40755,7 +40883,7 @@
       </c>
       <c r="B1265" s="1" t="inlineStr">
         <is>
-          <t>[kwestjoˈnaɾ] 问题&lt;动&gt;</t>
+          <t>[/kwestjoˈnaɾ/] 质疑；提问；对…提出异议&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1265" s="1" t="inlineStr">
@@ -40765,7 +40893,7 @@
       </c>
       <c r="D1265" s="1" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>质疑；提问；对…提出异议</t>
         </is>
       </c>
       <c r="E1265" s="1" t="inlineStr">
@@ -40883,7 +41011,7 @@
       </c>
       <c r="B1269" s="1" t="inlineStr">
         <is>
-          <t>[ˈala] 哈拉&lt;叹&gt;</t>
+          <t>[/ˈala/] 加油；快走（催促声）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C1269" s="1" t="inlineStr">
@@ -40893,7 +41021,7 @@
       </c>
       <c r="D1269" s="1" t="inlineStr">
         <is>
-          <t>哈拉</t>
+          <t>加油；快走（催促声）</t>
         </is>
       </c>
       <c r="E1269" s="1" t="inlineStr">
@@ -41299,7 +41427,7 @@
       </c>
       <c r="B1282" s="1" t="inlineStr">
         <is>
-          <t>[ˈare] 阿雷&lt;叹&gt;</t>
+          <t>[/ˈare/] 驾；快走（赶牲口用语）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C1282" s="1" t="inlineStr">
@@ -41309,7 +41437,7 @@
       </c>
       <c r="D1282" s="1" t="inlineStr">
         <is>
-          <t>阿雷</t>
+          <t>驾；快走（赶牲口用语）</t>
         </is>
       </c>
       <c r="E1282" s="1" t="inlineStr">
@@ -41491,7 +41619,7 @@
       </c>
       <c r="B1288" s="1" t="inlineStr">
         <is>
-          <t>[ˈmen] 男人&lt;名&gt;</t>
+          <t>[/ˈmen/] 傻瓜；笨蛋（墨西哥俚语）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1288" s="1" t="inlineStr">
@@ -41501,7 +41629,7 @@
       </c>
       <c r="D1288" s="1" t="inlineStr">
         <is>
-          <t>男人</t>
+          <t>傻瓜；笨蛋（墨西哥俚语）</t>
         </is>
       </c>
       <c r="E1288" s="1" t="inlineStr">
@@ -41523,7 +41651,7 @@
       </c>
       <c r="B1289" s="1" t="inlineStr">
         <is>
-          <t>[impoˈtente] 无助的&lt;形&gt;</t>
+          <t>[/impoˈtente/] 无力的，无能的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1289" s="1" t="inlineStr">
@@ -41533,7 +41661,7 @@
       </c>
       <c r="D1289" s="1" t="inlineStr">
         <is>
-          <t>无助的</t>
+          <t>无力的，无能的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1289" s="1" t="inlineStr">
@@ -41555,7 +41683,7 @@
       </c>
       <c r="B1290" s="1" t="inlineStr">
         <is>
-          <t>[kaʝeˈxeɾo] 街道&lt;名&gt;</t>
+          <t>[/kaʝeˈxeɾo/] 街道的；流浪的；街道图&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1290" s="1" t="inlineStr">
@@ -41565,7 +41693,7 @@
       </c>
       <c r="D1290" s="1" t="inlineStr">
         <is>
-          <t>街道</t>
+          <t>街道的；流浪的；街道图</t>
         </is>
       </c>
       <c r="E1290" s="1" t="inlineStr">
@@ -41587,7 +41715,7 @@
       </c>
       <c r="B1291" s="1" t="inlineStr">
         <is>
-          <t>[repaˈsaɾ] 评论&lt;动&gt;</t>
+          <t>[/repaˈsaɾ/] 复习；检查；熨烫&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1291" s="1" t="inlineStr">
@@ -41597,7 +41725,7 @@
       </c>
       <c r="D1291" s="1" t="inlineStr">
         <is>
-          <t>评论</t>
+          <t>复习；检查；熨烫</t>
         </is>
       </c>
       <c r="E1291" s="1" t="inlineStr">
@@ -41715,7 +41843,7 @@
       </c>
       <c r="B1295" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɾuxo] 女巫&lt;名&gt;</t>
+          <t>[/ˈbɾuxo/] 男巫；巫师&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1295" s="1" t="inlineStr">
@@ -41725,7 +41853,7 @@
       </c>
       <c r="D1295" s="1" t="inlineStr">
         <is>
-          <t>女巫</t>
+          <t>男巫；巫师</t>
         </is>
       </c>
       <c r="E1295" s="1" t="inlineStr">
@@ -41782,7 +41910,11 @@
           <t>可乐&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1297" s="1" t="inlineStr"/>
+      <c r="C1297" s="1" t="inlineStr">
+        <is>
+          <t>/ˌkokaˈkola/</t>
+        </is>
+      </c>
       <c r="D1297" s="1" t="inlineStr">
         <is>
           <t>可乐</t>
@@ -41906,7 +42038,11 @@
           <t>认真地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1301" s="1" t="inlineStr"/>
+      <c r="C1301" s="1" t="inlineStr">
+        <is>
+          <t>/enseɾjo/</t>
+        </is>
+      </c>
       <c r="D1301" s="1" t="inlineStr">
         <is>
           <t>认真地</t>
@@ -42603,7 +42739,7 @@
       </c>
       <c r="B1323" s="1" t="inlineStr">
         <is>
-          <t>[pɾoʝeɡˈtaɾ] 项目&lt;动&gt;</t>
+          <t>[/pɾoʝeɡˈtaɾ/] 投射；规划；放映&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1323" s="1" t="inlineStr">
@@ -42613,7 +42749,7 @@
       </c>
       <c r="D1323" s="1" t="inlineStr">
         <is>
-          <t>项目</t>
+          <t>投射；规划；放映</t>
         </is>
       </c>
       <c r="E1323" s="1" t="inlineStr">
@@ -42667,7 +42803,7 @@
       </c>
       <c r="B1325" s="1" t="inlineStr">
         <is>
-          <t>[estɾeˈsado] 强调&lt;形&gt;</t>
+          <t>[/estɾeˈsado/] 紧张的；有压力的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1325" s="1" t="inlineStr">
@@ -42677,7 +42813,7 @@
       </c>
       <c r="D1325" s="1" t="inlineStr">
         <is>
-          <t>强调</t>
+          <t>紧张的；有压力的</t>
         </is>
       </c>
       <c r="E1325" s="1" t="inlineStr">
@@ -43051,7 +43187,7 @@
       </c>
       <c r="B1337" s="1" t="inlineStr">
         <is>
-          <t>[piˈsaɾ] 步骤&lt;动&gt;</t>
+          <t>[/piˈsaɾ/] 踩；踏&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1337" s="1" t="inlineStr">
@@ -43061,7 +43197,7 @@
       </c>
       <c r="D1337" s="1" t="inlineStr">
         <is>
-          <t>步骤</t>
+          <t>踩；踏</t>
         </is>
       </c>
       <c r="E1337" s="1" t="inlineStr">
@@ -43470,7 +43606,11 @@
           <t>跳跃&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1350" s="1" t="inlineStr"/>
+      <c r="C1350" s="1" t="inlineStr">
+        <is>
+          <t>/ˈsaltos/</t>
+        </is>
+      </c>
       <c r="D1350" s="1" t="inlineStr">
         <is>
           <t>跳跃</t>
@@ -44039,7 +44179,7 @@
       </c>
       <c r="B1368" s="1" t="inlineStr">
         <is>
-          <t>[ˈkofɾe] 胸部&lt;名&gt;</t>
+          <t>[/ˈkofɾe/] 箱子；宝箱&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1368" s="1" t="inlineStr">
@@ -44049,7 +44189,7 @@
       </c>
       <c r="D1368" s="1" t="inlineStr">
         <is>
-          <t>胸部</t>
+          <t>箱子；宝箱</t>
         </is>
       </c>
       <c r="E1368" s="1" t="inlineStr">
@@ -44394,7 +44534,11 @@
           <t>f.&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1379" s="1" t="inlineStr"/>
+      <c r="C1379" s="1" t="inlineStr">
+        <is>
+          <t>/femeˈnino/</t>
+        </is>
+      </c>
       <c r="D1379" s="1" t="inlineStr">
         <is>
           <t>f.</t>
@@ -44579,7 +44723,7 @@
       </c>
       <c r="B1385" s="1" t="inlineStr">
         <is>
-          <t>[ˈpisa] 步骤&lt;名&gt;</t>
+          <t>[/ˈpisa/] 踩踏；脚步&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1385" s="1" t="inlineStr">
@@ -44589,7 +44733,7 @@
       </c>
       <c r="D1385" s="1" t="inlineStr">
         <is>
-          <t>步骤</t>
+          <t>踩踏；脚步</t>
         </is>
       </c>
       <c r="E1385" s="1" t="inlineStr">
@@ -45443,7 +45587,7 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>[xaˈleo] 大惊小怪&lt;名&gt;</t>
+          <t>[/xaˈleo/] 喧闹，吵闹；骚乱&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1412" s="1" t="inlineStr">
@@ -45453,7 +45597,7 @@
       </c>
       <c r="D1412" s="1" t="inlineStr">
         <is>
-          <t>大惊小怪</t>
+          <t>喧闹，吵闹；骚乱&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1412" s="1" t="inlineStr">
@@ -45475,7 +45619,7 @@
       </c>
       <c r="B1413" s="1" t="inlineStr">
         <is>
-          <t>[ˈplant͡ʃa] 铁&lt;名&gt;</t>
+          <t>[/ˈplant͡ʃa/] 熨斗；木板&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1413" s="1" t="inlineStr">
@@ -45485,7 +45629,7 @@
       </c>
       <c r="D1413" s="1" t="inlineStr">
         <is>
-          <t>铁</t>
+          <t>熨斗；木板</t>
         </is>
       </c>
       <c r="E1413" s="1" t="inlineStr">
@@ -45702,10 +45846,14 @@
           <t>聪明的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1420" s="1" t="inlineStr"/>
+      <c r="C1420" s="1" t="inlineStr">
+        <is>
+          <t>/smˈaɾt/</t>
+        </is>
+      </c>
       <c r="D1420" s="1" t="inlineStr">
         <is>
-          <t>聪明的</t>
+          <t>非西班牙语词汇，应删除或标注为英语外来词</t>
         </is>
       </c>
       <c r="E1420" s="1" t="inlineStr">
@@ -45791,7 +45939,7 @@
       </c>
       <c r="B1423" s="1" t="inlineStr">
         <is>
-          <t>[ˈplaʝo] 海滩&lt;名&gt;</t>
+          <t>[/ˈplaʝo/] 非标准西班牙语词；若为方言/俚语，指沿海居民或浅滩相关，'平坦的'不正确&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1423" s="1" t="inlineStr">
@@ -45801,7 +45949,7 @@
       </c>
       <c r="D1423" s="1" t="inlineStr">
         <is>
-          <t>海滩</t>
+          <t>非标准西班牙语词；若为方言/俚语，指沿海居民或浅滩相关，'平坦的'不正确</t>
         </is>
       </c>
       <c r="E1423" s="1" t="inlineStr">
@@ -46338,7 +46486,11 @@
           <t>金色&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1440" s="1" t="inlineStr"/>
+      <c r="C1440" s="1" t="inlineStr">
+        <is>
+          <t>/ɡˈolden/</t>
+        </is>
+      </c>
       <c r="D1440" s="1" t="inlineStr">
         <is>
           <t>金色</t>
@@ -46814,7 +46966,11 @@
           <t>呃&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1455" s="1" t="inlineStr"/>
+      <c r="C1455" s="1" t="inlineStr">
+        <is>
+          <t>/uf/</t>
+        </is>
+      </c>
       <c r="D1455" s="1" t="inlineStr">
         <is>
           <t>呃</t>
@@ -46903,7 +47059,7 @@
       </c>
       <c r="B1458" s="1" t="inlineStr">
         <is>
-          <t>[ˈkwelɡe] 挂断电话&lt;名&gt;</t>
+          <t>[/ˈkwelɡe/] 悬挂；（电脑等）死机；懒散的人&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1458" s="1" t="inlineStr">
@@ -46913,7 +47069,7 @@
       </c>
       <c r="D1458" s="1" t="inlineStr">
         <is>
-          <t>挂断电话</t>
+          <t>悬挂；（电脑等）死机；懒散的人&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1458" s="1" t="inlineStr">
@@ -46935,7 +47091,7 @@
       </c>
       <c r="B1459" s="1" t="inlineStr">
         <is>
-          <t>[ˈbledo] 该死的&lt;名&gt;</t>
+          <t>[/ˈbledo/] 藜草；野苋（植物）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1459" s="1" t="inlineStr">
@@ -46945,7 +47101,7 @@
       </c>
       <c r="D1459" s="1" t="inlineStr">
         <is>
-          <t>该死的</t>
+          <t>藜草；野苋（植物）</t>
         </is>
       </c>
       <c r="E1459" s="1" t="inlineStr">
@@ -46999,7 +47155,7 @@
       </c>
       <c r="B1461" s="1" t="inlineStr">
         <is>
-          <t>[estaθjoˈnaɾ] 公园&lt;动&gt;</t>
+          <t>[/estaθjoˈnaɾ/] 停放（车辆）；停靠&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1461" s="1" t="inlineStr">
@@ -47009,7 +47165,7 @@
       </c>
       <c r="D1461" s="1" t="inlineStr">
         <is>
-          <t>公园</t>
+          <t>停放（车辆）；停靠</t>
         </is>
       </c>
       <c r="E1461" s="1" t="inlineStr">
@@ -47895,7 +48051,7 @@
       </c>
       <c r="B1489" s="1" t="inlineStr">
         <is>
-          <t>[inkluˈsibe] 甚至&lt;副&gt;</t>
+          <t>[/inkluˈsibe/] 包括在内；包含&lt;adv&gt;</t>
         </is>
       </c>
       <c r="C1489" s="1" t="inlineStr">
@@ -47905,7 +48061,7 @@
       </c>
       <c r="D1489" s="1" t="inlineStr">
         <is>
-          <t>甚至</t>
+          <t>包括在内；包含</t>
         </is>
       </c>
       <c r="E1489" s="1" t="inlineStr">
@@ -48506,10 +48662,14 @@
           <t>鸡舍&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1508" s="1" t="inlineStr"/>
+      <c r="C1508" s="1" t="inlineStr">
+        <is>
+          <t>/koˈop/</t>
+        </is>
+      </c>
       <c r="D1508" s="1" t="inlineStr">
         <is>
-          <t>鸡舍</t>
+          <t>gallinero（coop为英语词，非西班牙语）</t>
         </is>
       </c>
       <c r="E1508" s="1" t="inlineStr">
@@ -48819,7 +48979,7 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>[ˈkolt] 小马&lt;名&gt;</t>
+          <t>[/ˈkolt/] 幼马，小雄马&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1518" s="1" t="inlineStr">
@@ -48829,7 +48989,7 @@
       </c>
       <c r="D1518" s="1" t="inlineStr">
         <is>
-          <t>小马</t>
+          <t>幼马，小雄马</t>
         </is>
       </c>
       <c r="E1518" s="1" t="inlineStr">
@@ -48851,7 +49011,7 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>[ˈkastɾo] 卡斯特罗&lt;名&gt;</t>
+          <t>[/ˈkastɾo/] （史前）山寨，堡垒遗址&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1519" s="1" t="inlineStr">
@@ -48861,7 +49021,7 @@
       </c>
       <c r="D1519" s="1" t="inlineStr">
         <is>
-          <t>卡斯特罗</t>
+          <t>（史前）山寨，堡垒遗址&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1519" s="1" t="inlineStr">
@@ -48947,7 +49107,7 @@
       </c>
       <c r="B1522" s="1" t="inlineStr">
         <is>
-          <t>[ˈporo] 联合&lt;名&gt;</t>
+          <t>[/ˈporo/] 大麻烟卷；棍棒&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1522" s="1" t="inlineStr">
@@ -48957,7 +49117,7 @@
       </c>
       <c r="D1522" s="1" t="inlineStr">
         <is>
-          <t>联合</t>
+          <t>大麻烟卷；棍棒</t>
         </is>
       </c>
       <c r="E1522" s="1" t="inlineStr">
@@ -49078,7 +49238,11 @@
           <t>笑&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1526" s="1" t="inlineStr"/>
+      <c r="C1526" s="1" t="inlineStr">
+        <is>
+          <t>/ɾeˈiɾ/</t>
+        </is>
+      </c>
       <c r="D1526" s="1" t="inlineStr">
         <is>
           <t>笑</t>
@@ -49231,7 +49395,7 @@
       </c>
       <c r="B1531" s="1" t="inlineStr">
         <is>
-          <t>[ˈʝanki] 洋基队&lt;名&gt;</t>
+          <t>[/ˈʝanki/] 美国佬；北方佬&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1531" s="1" t="inlineStr">
@@ -49241,7 +49405,7 @@
       </c>
       <c r="D1531" s="1" t="inlineStr">
         <is>
-          <t>洋基队</t>
+          <t>美国佬；北方佬&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1531" s="1" t="inlineStr">
@@ -49583,7 +49747,7 @@
       </c>
       <c r="B1542" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾaɡa] 燕子&lt;名&gt;</t>
+          <t>[/ˈtɾaɡa/] 吞咽；豪饮&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1542" s="1" t="inlineStr">
@@ -49593,7 +49757,7 @@
       </c>
       <c r="D1542" s="1" t="inlineStr">
         <is>
-          <t>燕子</t>
+          <t>吞咽；豪饮&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1542" s="1" t="inlineStr">
@@ -49743,7 +49907,7 @@
       </c>
       <c r="B1547" s="1" t="inlineStr">
         <is>
-          <t>[ˈko] 共&lt;名&gt;</t>
+          <t>[/ˈko/] 共同（前缀）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1547" s="1" t="inlineStr">
@@ -49753,7 +49917,7 @@
       </c>
       <c r="D1547" s="1" t="inlineStr">
         <is>
-          <t>共</t>
+          <t>共同（前缀）</t>
         </is>
       </c>
       <c r="E1547" s="1" t="inlineStr">
@@ -49807,7 +49971,7 @@
       </c>
       <c r="B1549" s="1" t="inlineStr">
         <is>
-          <t>[estudjanˈtil] 学生&lt;形&gt;</t>
+          <t>[/estudjanˈtil/] 学生的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1549" s="1" t="inlineStr">
@@ -49817,7 +49981,7 @@
       </c>
       <c r="D1549" s="1" t="inlineStr">
         <is>
-          <t>学生</t>
+          <t>学生的</t>
         </is>
       </c>
       <c r="E1549" s="1" t="inlineStr">
@@ -50607,7 +50771,7 @@
       </c>
       <c r="B1574" s="1" t="inlineStr">
         <is>
-          <t>[estomaˈɡaɾ] 胃&lt;动&gt;</t>
+          <t>[/estomaˈɡaɾ/] 使恶心；使厌恶&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1574" s="1" t="inlineStr">
@@ -50617,7 +50781,7 @@
       </c>
       <c r="D1574" s="1" t="inlineStr">
         <is>
-          <t>胃</t>
+          <t>使恶心；使厌恶</t>
         </is>
       </c>
       <c r="E1574" s="1" t="inlineStr">
@@ -50639,7 +50803,7 @@
       </c>
       <c r="B1575" s="1" t="inlineStr">
         <is>
-          <t>[ˈpoɾta] 持有人&lt;名&gt;</t>
+          <t>[/ˈpoɾta/] 门；大门&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1575" s="1" t="inlineStr">
@@ -50649,7 +50813,7 @@
       </c>
       <c r="D1575" s="1" t="inlineStr">
         <is>
-          <t>持有人</t>
+          <t>门；大门&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1575" s="1" t="inlineStr">
@@ -50770,7 +50934,11 @@
           <t>僵尸&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1579" s="1" t="inlineStr"/>
+      <c r="C1579" s="1" t="inlineStr">
+        <is>
+          <t>/ˈsombi/</t>
+        </is>
+      </c>
       <c r="D1579" s="1" t="inlineStr">
         <is>
           <t>僵尸</t>
@@ -51054,7 +51222,11 @@
           <t>再见&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C1588" s="1" t="inlineStr"/>
+      <c r="C1588" s="1" t="inlineStr">
+        <is>
+          <t>/θiˈao/</t>
+        </is>
+      </c>
       <c r="D1588" s="1" t="inlineStr">
         <is>
           <t>再见</t>
@@ -51143,7 +51315,7 @@
       </c>
       <c r="B1591" s="1" t="inlineStr">
         <is>
-          <t>[emiˈtiɾ] 演员表&lt;动&gt;</t>
+          <t>[/emiˈtiɾ/] 发射；播送；发行&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1591" s="1" t="inlineStr">
@@ -51153,7 +51325,7 @@
       </c>
       <c r="D1591" s="1" t="inlineStr">
         <is>
-          <t>演员表</t>
+          <t>发射；播送；发行</t>
         </is>
       </c>
       <c r="E1591" s="1" t="inlineStr">
@@ -51175,7 +51347,7 @@
       </c>
       <c r="B1592" s="1" t="inlineStr">
         <is>
-          <t>[ˈpos] 位置&lt;名&gt;</t>
+          <t>[/ˈpos/] （古语）那么，既然&lt;副&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1592" s="1" t="inlineStr">
@@ -51185,7 +51357,7 @@
       </c>
       <c r="D1592" s="1" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>（古语）那么，既然&lt;副&gt;</t>
         </is>
       </c>
       <c r="E1592" s="1" t="inlineStr">
@@ -51463,13 +51635,17 @@
       </c>
       <c r="B1601" s="1" t="inlineStr">
         <is>
-          <t>比利时&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C1601" s="1" t="inlineStr"/>
+          <t>[[ˈbel.xi.ko]] 比利时的&lt;形&gt;（常用形式为belga）&lt;adj&gt;</t>
+        </is>
+      </c>
+      <c r="C1601" s="1" t="inlineStr">
+        <is>
+          <t>/bˈelxiko/</t>
+        </is>
+      </c>
       <c r="D1601" s="1" t="inlineStr">
         <is>
-          <t>比利时</t>
+          <t>比利时的&lt;形&gt;（常用形式为belga）</t>
         </is>
       </c>
       <c r="E1601" s="1" t="inlineStr">
@@ -51491,7 +51667,7 @@
       </c>
       <c r="B1602" s="1" t="inlineStr">
         <is>
-          <t>[tɾansboɾdaˈdoɾ] 渡轮&lt;名&gt;</t>
+          <t>[/tɾansboɾdaˈdoɾ/] 航天飞机；渡轮&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1602" s="1" t="inlineStr">
@@ -51501,7 +51677,7 @@
       </c>
       <c r="D1602" s="1" t="inlineStr">
         <is>
-          <t>渡轮</t>
+          <t>航天飞机；渡轮&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1602" s="1" t="inlineStr">
@@ -51942,7 +52118,11 @@
           <t>直&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1616" s="1" t="inlineStr"/>
+      <c r="C1616" s="1" t="inlineStr">
+        <is>
+          <t>/etˈeɾo/</t>
+        </is>
+      </c>
       <c r="D1616" s="1" t="inlineStr">
         <is>
           <t>直</t>
@@ -52735,7 +52915,7 @@
       </c>
       <c r="B1641" s="1" t="inlineStr">
         <is>
-          <t>[ˈbaɾɡa] 瓦尔加&lt;名&gt;</t>
+          <t>[/ˈbaɾɡa/] 非标准词；或为人名（瓦尔加）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1641" s="1" t="inlineStr">
@@ -52745,7 +52925,7 @@
       </c>
       <c r="D1641" s="1" t="inlineStr">
         <is>
-          <t>瓦尔加</t>
+          <t>非标准词；或为人名（瓦尔加）</t>
         </is>
       </c>
       <c r="E1641" s="1" t="inlineStr">
@@ -53439,13 +53619,17 @@
       </c>
       <c r="B1663" s="1" t="inlineStr">
         <is>
-          <t>泰&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1663" s="1" t="inlineStr"/>
+          <t>[[ˈtai̯] 泰；泰语&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1663" s="1" t="inlineStr">
+        <is>
+          <t>/tˈai/</t>
+        </is>
+      </c>
       <c r="D1663" s="1" t="inlineStr">
         <is>
-          <t>泰</t>
+          <t>泰；泰语</t>
         </is>
       </c>
       <c r="E1663" s="1" t="inlineStr">
@@ -53691,7 +53875,7 @@
       </c>
       <c r="B1671" s="1" t="inlineStr">
         <is>
-          <t>[adabˈtaɾ] 适应&lt;动&gt;</t>
+          <t>[/adabˈtaɾ/] 使适应；改编&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1671" s="1" t="inlineStr">
@@ -53701,7 +53885,7 @@
       </c>
       <c r="D1671" s="1" t="inlineStr">
         <is>
-          <t>适应</t>
+          <t>使适应；改编&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1671" s="1" t="inlineStr">
@@ -53819,13 +54003,17 @@
       </c>
       <c r="B1675" s="1" t="inlineStr">
         <is>
-          <t>张柏芝&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1675" s="1" t="inlineStr"/>
+          <t>[[θeˈθi.lja] 塞西莉亚（女子名）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1675" s="1" t="inlineStr">
+        <is>
+          <t>/θeθilˈia/</t>
+        </is>
+      </c>
       <c r="D1675" s="1" t="inlineStr">
         <is>
-          <t>张柏芝</t>
+          <t>塞西莉亚（女子名）</t>
         </is>
       </c>
       <c r="E1675" s="1" t="inlineStr">
@@ -54074,7 +54262,11 @@
           <t>奇妙地&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1683" s="1" t="inlineStr"/>
+      <c r="C1683" s="1" t="inlineStr">
+        <is>
+          <t>/estupendamente/</t>
+        </is>
+      </c>
       <c r="D1683" s="1" t="inlineStr">
         <is>
           <t>奇妙地</t>
@@ -54294,7 +54486,11 @@
           <t>年轻人&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1690" s="1" t="inlineStr"/>
+      <c r="C1690" s="1" t="inlineStr">
+        <is>
+          <t>/xobˈenes/</t>
+        </is>
+      </c>
       <c r="D1690" s="1" t="inlineStr">
         <is>
           <t>年轻人</t>
@@ -54578,7 +54774,11 @@
           <t>车库&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1699" s="1" t="inlineStr"/>
+      <c r="C1699" s="1" t="inlineStr">
+        <is>
+          <t>/ɡaɾˈaxe/</t>
+        </is>
+      </c>
       <c r="D1699" s="1" t="inlineStr">
         <is>
           <t>车库</t>
@@ -55115,7 +55315,7 @@
       </c>
       <c r="B1716" s="1" t="inlineStr">
         <is>
-          <t>[akoxeˈdoɾ] 舒适&lt;形&gt;</t>
+          <t>[/akoxeˈdoɾ/] 热情好客的；温馨的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1716" s="1" t="inlineStr">
@@ -55125,7 +55325,7 @@
       </c>
       <c r="D1716" s="1" t="inlineStr">
         <is>
-          <t>舒适</t>
+          <t>热情好客的；温馨的</t>
         </is>
       </c>
       <c r="E1716" s="1" t="inlineStr">
@@ -55438,7 +55638,11 @@
           <t>新闻学&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1726" s="1" t="inlineStr"/>
+      <c r="C1726" s="1" t="inlineStr">
+        <is>
+          <t>/peɾjoˈðismo/</t>
+        </is>
+      </c>
       <c r="D1726" s="1" t="inlineStr">
         <is>
           <t>新闻学</t>
@@ -56007,7 +56211,7 @@
       </c>
       <c r="B1744" s="1" t="inlineStr">
         <is>
-          <t>[esˈtaka] 股份&lt;名&gt;</t>
+          <t>[/esˈtaka/] 桩；木桩&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1744" s="1" t="inlineStr">
@@ -56017,7 +56221,7 @@
       </c>
       <c r="D1744" s="1" t="inlineStr">
         <is>
-          <t>股份</t>
+          <t>桩；木桩</t>
         </is>
       </c>
       <c r="E1744" s="1" t="inlineStr">
@@ -56042,7 +56246,11 @@
           <t>房地产&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1745" s="1" t="inlineStr"/>
+      <c r="C1745" s="1" t="inlineStr">
+        <is>
+          <t>/inmobiˈljaɾjo/</t>
+        </is>
+      </c>
       <c r="D1745" s="1" t="inlineStr">
         <is>
           <t>房地产</t>
@@ -56163,7 +56371,7 @@
       </c>
       <c r="B1749" s="1" t="inlineStr">
         <is>
-          <t>[baˈboɾ] 港口&lt;名&gt;</t>
+          <t>[/baˈboɾ/] 左舷&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1749" s="1" t="inlineStr">
@@ -56173,7 +56381,7 @@
       </c>
       <c r="D1749" s="1" t="inlineStr">
         <is>
-          <t>港口</t>
+          <t>左舷</t>
         </is>
       </c>
       <c r="E1749" s="1" t="inlineStr">
@@ -56259,7 +56467,7 @@
       </c>
       <c r="B1752" s="1" t="inlineStr">
         <is>
-          <t>[reˈθinto] 外壳&lt;名&gt;</t>
+          <t>[/reˈθinto/] 场所；围地；馆区&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1752" s="1" t="inlineStr">
@@ -56269,7 +56477,7 @@
       </c>
       <c r="D1752" s="1" t="inlineStr">
         <is>
-          <t>外壳</t>
+          <t>场所；围地；馆区</t>
         </is>
       </c>
       <c r="E1752" s="1" t="inlineStr">
@@ -56515,13 +56723,17 @@
       </c>
       <c r="B1760" s="1" t="inlineStr">
         <is>
-          <t>加州&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1760" s="1" t="inlineStr"/>
+          <t>[[ka] 约（circa 缩写）；公司（compañía 缩写）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1760" s="1" t="inlineStr">
+        <is>
+          <t>/ka/</t>
+        </is>
+      </c>
       <c r="D1760" s="1" t="inlineStr">
         <is>
-          <t>加州</t>
+          <t>约（circa 缩写）；公司（compañía 缩写）</t>
         </is>
       </c>
       <c r="E1760" s="1" t="inlineStr">
@@ -56546,7 +56758,11 @@
           <t>东北&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1761" s="1" t="inlineStr"/>
+      <c r="C1761" s="1" t="inlineStr">
+        <is>
+          <t>/noɾˈeste/</t>
+        </is>
+      </c>
       <c r="D1761" s="1" t="inlineStr">
         <is>
           <t>东北</t>
@@ -56731,7 +56947,7 @@
       </c>
       <c r="B1767" s="1" t="inlineStr">
         <is>
-          <t>[ronˈdaɾ] 悬停&lt;动&gt;</t>
+          <t>[/ronˈdaɾ/] 徘徊；巡逻；盘旋&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1767" s="1" t="inlineStr">
@@ -56741,7 +56957,7 @@
       </c>
       <c r="D1767" s="1" t="inlineStr">
         <is>
-          <t>悬停</t>
+          <t>徘徊；巡逻；盘旋</t>
         </is>
       </c>
       <c r="E1767" s="1" t="inlineStr">
@@ -57118,7 +57334,11 @@
           <t>小男孩&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1779" s="1" t="inlineStr"/>
+      <c r="C1779" s="1" t="inlineStr">
+        <is>
+          <t>/tʃikiʎo/</t>
+        </is>
+      </c>
       <c r="D1779" s="1" t="inlineStr">
         <is>
           <t>小男孩</t>
@@ -57143,7 +57363,7 @@
       </c>
       <c r="B1780" s="1" t="inlineStr">
         <is>
-          <t>[kaˈroθa] 浮动&lt;名&gt;</t>
+          <t>[kaˈroθa] 四轮马车；彩车&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1780" s="1" t="inlineStr">
@@ -57153,7 +57373,7 @@
       </c>
       <c r="D1780" s="1" t="inlineStr">
         <is>
-          <t>浮动</t>
+          <t>四轮马车；彩车</t>
         </is>
       </c>
       <c r="E1780" s="1" t="inlineStr">
@@ -57207,7 +57427,7 @@
       </c>
       <c r="B1782" s="1" t="inlineStr">
         <is>
-          <t>[kaɾˈtut͡ʃo] 墨盒&lt;名&gt;</t>
+          <t>[/kaɾˈtut͡ʃo/] 弹药筒；子弹壳；墨盒&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1782" s="1" t="inlineStr">
@@ -57217,7 +57437,7 @@
       </c>
       <c r="D1782" s="1" t="inlineStr">
         <is>
-          <t>墨盒</t>
+          <t>弹药筒；子弹壳；墨盒&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1782" s="1" t="inlineStr">
@@ -57530,7 +57750,11 @@
           <t>笑了&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1792" s="1" t="inlineStr"/>
+      <c r="C1792" s="1" t="inlineStr">
+        <is>
+          <t>/ˈrjo/</t>
+        </is>
+      </c>
       <c r="D1792" s="1" t="inlineStr">
         <is>
           <t>笑了</t>
@@ -57686,7 +57910,11 @@
           <t>诺贝尔&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1797" s="1" t="inlineStr"/>
+      <c r="C1797" s="1" t="inlineStr">
+        <is>
+          <t>/nobˈel/</t>
+        </is>
+      </c>
       <c r="D1797" s="1" t="inlineStr">
         <is>
           <t>诺贝尔</t>
@@ -58287,7 +58515,7 @@
       </c>
       <c r="B1816" s="1" t="inlineStr">
         <is>
-          <t>[komˈplot] 情节&lt;名&gt;</t>
+          <t>[komˈplot] 阴谋；密谋&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1816" s="1" t="inlineStr">
@@ -58297,7 +58525,7 @@
       </c>
       <c r="D1816" s="1" t="inlineStr">
         <is>
-          <t>情节</t>
+          <t>阴谋；密谋</t>
         </is>
       </c>
       <c r="E1816" s="1" t="inlineStr">
@@ -58639,7 +58867,7 @@
       </c>
       <c r="B1827" s="1" t="inlineStr">
         <is>
-          <t>[amaˈθona] 亚马逊&lt;名&gt;</t>
+          <t>[amaˈθona] 女骑士；亚马逊女战士&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1827" s="1" t="inlineStr">
@@ -58649,7 +58877,7 @@
       </c>
       <c r="D1827" s="1" t="inlineStr">
         <is>
-          <t>亚马逊</t>
+          <t>女骑士；亚马逊女战士</t>
         </is>
       </c>
       <c r="E1827" s="1" t="inlineStr">
@@ -59439,7 +59667,7 @@
       </c>
       <c r="B1852" s="1" t="inlineStr">
         <is>
-          <t>[θeˈɾiʝa] 比赛&lt;名&gt;</t>
+          <t>[θeˈɾiʝa] 火柴&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1852" s="1" t="inlineStr">
@@ -59449,7 +59677,7 @@
       </c>
       <c r="D1852" s="1" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>火柴</t>
         </is>
       </c>
       <c r="E1852" s="1" t="inlineStr">
@@ -59503,7 +59731,7 @@
       </c>
       <c r="B1854" s="1" t="inlineStr">
         <is>
-          <t>[abuˈriɾ] 钻孔&lt;动&gt;</t>
+          <t>[abuˈriɾ] 使厌烦；使厌倦&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1854" s="1" t="inlineStr">
@@ -59513,7 +59741,7 @@
       </c>
       <c r="D1854" s="1" t="inlineStr">
         <is>
-          <t>钻孔</t>
+          <t>使厌烦；使厌倦</t>
         </is>
       </c>
       <c r="E1854" s="1" t="inlineStr">
@@ -59599,13 +59827,17 @@
       </c>
       <c r="B1857" s="1" t="inlineStr">
         <is>
-          <t>与&lt;介&gt;</t>
-        </is>
-      </c>
-      <c r="C1857" s="1" t="inlineStr"/>
+          <t>对；对抗&lt;介&gt;</t>
+        </is>
+      </c>
+      <c r="C1857" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkontɾa/</t>
+        </is>
+      </c>
       <c r="D1857" s="1" t="inlineStr">
         <is>
-          <t>与</t>
+          <t>对；对抗</t>
         </is>
       </c>
       <c r="E1857" s="1" t="inlineStr">
@@ -59659,13 +59891,17 @@
       </c>
       <c r="B1859" s="1" t="inlineStr">
         <is>
-          <t>琪琪&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1859" s="1" t="inlineStr"/>
+          <t>[[ˈkiki] 监狱（俚语）；人名&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1859" s="1" t="inlineStr">
+        <is>
+          <t>/kˈiki/</t>
+        </is>
+      </c>
       <c r="D1859" s="1" t="inlineStr">
         <is>
-          <t>琪琪</t>
+          <t>监狱（俚语）；人名</t>
         </is>
       </c>
       <c r="E1859" s="1" t="inlineStr">
@@ -59911,7 +60147,7 @@
       </c>
       <c r="B1867" s="1" t="inlineStr">
         <is>
-          <t>[raθoˈnaɾ] 原因&lt;动&gt;</t>
+          <t>[raθoˈnaɾ] 推理；思考；讲道理&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1867" s="1" t="inlineStr">
@@ -59921,7 +60157,7 @@
       </c>
       <c r="D1867" s="1" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>推理；思考；讲道理</t>
         </is>
       </c>
       <c r="E1867" s="1" t="inlineStr">
@@ -59943,7 +60179,7 @@
       </c>
       <c r="B1868" s="1" t="inlineStr">
         <is>
-          <t>[ˈraund] 圆形&lt;名&gt;</t>
+          <t>[ˈraund] 回合；轮次&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1868" s="1" t="inlineStr">
@@ -59953,7 +60189,7 @@
       </c>
       <c r="D1868" s="1" t="inlineStr">
         <is>
-          <t>圆形</t>
+          <t>回合；轮次</t>
         </is>
       </c>
       <c r="E1868" s="1" t="inlineStr">
@@ -60391,13 +60627,17 @@
       </c>
       <c r="B1882" s="1" t="inlineStr">
         <is>
-          <t>信仰&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1882" s="1" t="inlineStr"/>
+          <t>[[ˈfe]] fe 信仰&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1882" s="1" t="inlineStr">
+        <is>
+          <t>/fˈe/</t>
+        </is>
+      </c>
       <c r="D1882" s="1" t="inlineStr">
         <is>
-          <t>信仰</t>
+          <t>fe 信仰&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1882" s="1" t="inlineStr">
@@ -61059,7 +61299,7 @@
       </c>
       <c r="B1903" s="1" t="inlineStr">
         <is>
-          <t>[kaˈʝao] 闭嘴&lt;名&gt;</t>
+          <t>[kaˈʝao] 沉默的；安静的；卡亚俄（秘鲁港市）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1903" s="1" t="inlineStr">
@@ -61069,7 +61309,7 @@
       </c>
       <c r="D1903" s="1" t="inlineStr">
         <is>
-          <t>闭嘴</t>
+          <t>沉默的；安静的；卡亚俄（秘鲁港市）</t>
         </is>
       </c>
       <c r="E1903" s="1" t="inlineStr">
@@ -61507,7 +61747,7 @@
       </c>
       <c r="B1917" s="1" t="inlineStr">
         <is>
-          <t>[ˈakɾe] 英亩&lt;名&gt;</t>
+          <t>[/ˈakɾe/] 辛辣的&lt;形&gt;；刺激的&lt;形&gt;；刻薄的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1917" s="1" t="inlineStr">
@@ -61517,7 +61757,7 @@
       </c>
       <c r="D1917" s="1" t="inlineStr">
         <is>
-          <t>英亩</t>
+          <t>辛辣的&lt;形&gt;；刺激的&lt;形&gt;；刻薄的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1917" s="1" t="inlineStr">
@@ -61571,7 +61811,7 @@
       </c>
       <c r="B1919" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡanɡa] 讨价还价&lt;名&gt;</t>
+          <t>[ˈɡanɡa] 便宜货；划算的交易&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1919" s="1" t="inlineStr">
@@ -61581,7 +61821,7 @@
       </c>
       <c r="D1919" s="1" t="inlineStr">
         <is>
-          <t>讨价还价</t>
+          <t>便宜货；划算的交易</t>
         </is>
       </c>
       <c r="E1919" s="1" t="inlineStr">
@@ -61606,7 +61846,11 @@
           <t>花花公子&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1920" s="1" t="inlineStr"/>
+      <c r="C1920" s="1" t="inlineStr">
+        <is>
+          <t>/plajbˈoj/</t>
+        </is>
+      </c>
       <c r="D1920" s="1" t="inlineStr">
         <is>
           <t>花花公子</t>
@@ -61663,7 +61907,7 @@
       </c>
       <c r="B1922" s="1" t="inlineStr">
         <is>
-          <t>[reˈkluta] 招募&lt;名&gt;</t>
+          <t>[/reˈkluta/] 新兵&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1922" s="1" t="inlineStr">
@@ -61673,7 +61917,7 @@
       </c>
       <c r="D1922" s="1" t="inlineStr">
         <is>
-          <t>招募</t>
+          <t>新兵&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1922" s="1" t="inlineStr">
@@ -61727,7 +61971,7 @@
       </c>
       <c r="B1924" s="1" t="inlineStr">
         <is>
-          <t>[ˈpinɡ] 平&lt;名&gt;</t>
+          <t>[ˈpinɡ] 乒声；网络延迟&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1924" s="1" t="inlineStr">
@@ -61737,7 +61981,7 @@
       </c>
       <c r="D1924" s="1" t="inlineStr">
         <is>
-          <t>平</t>
+          <t>乒声；网络延迟</t>
         </is>
       </c>
       <c r="E1924" s="1" t="inlineStr">
@@ -62111,7 +62355,7 @@
       </c>
       <c r="B1936" s="1" t="inlineStr">
         <is>
-          <t>[suˈplente] 替代品&lt;名&gt;</t>
+          <t>[/suˈplente/] 替补者&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1936" s="1" t="inlineStr">
@@ -62121,7 +62365,7 @@
       </c>
       <c r="D1936" s="1" t="inlineStr">
         <is>
-          <t>替代品</t>
+          <t>替补者&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1936" s="1" t="inlineStr">
@@ -62655,7 +62899,7 @@
       </c>
       <c r="B1953" s="1" t="inlineStr">
         <is>
-          <t>[ˈmauɾa] 毛拉&lt;名&gt;</t>
+          <t>[/ˈmauɾa/] 摩尔女人（mauro的阴性形式）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1953" s="1" t="inlineStr">
@@ -62665,7 +62909,7 @@
       </c>
       <c r="D1953" s="1" t="inlineStr">
         <is>
-          <t>毛拉</t>
+          <t>摩尔女人（mauro的阴性形式）</t>
         </is>
       </c>
       <c r="E1953" s="1" t="inlineStr">
@@ -62911,7 +63155,7 @@
       </c>
       <c r="B1961" s="1" t="inlineStr">
         <is>
-          <t>[ˈsensei] 老师&lt;名&gt;</t>
+          <t>[/ˈsensei/] 老师；师傅；先生&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1961" s="1" t="inlineStr">
@@ -62921,7 +63165,7 @@
       </c>
       <c r="D1961" s="1" t="inlineStr">
         <is>
-          <t>老师</t>
+          <t>老师；师傅；先生</t>
         </is>
       </c>
       <c r="E1961" s="1" t="inlineStr">
@@ -63039,7 +63283,7 @@
       </c>
       <c r="B1965" s="1" t="inlineStr">
         <is>
-          <t>[rekauˈdaɾ] 提高&lt;动&gt;</t>
+          <t>[/rekauˈdaɾ/] 征收；筹集（款项）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1965" s="1" t="inlineStr">
@@ -63049,7 +63293,7 @@
       </c>
       <c r="D1965" s="1" t="inlineStr">
         <is>
-          <t>提高</t>
+          <t>征收；筹集（款项）</t>
         </is>
       </c>
       <c r="E1965" s="1" t="inlineStr">
@@ -63551,7 +63795,7 @@
       </c>
       <c r="B1981" s="1" t="inlineStr">
         <is>
-          <t>[laˈtino] 拉丁语&lt;名&gt;</t>
+          <t>[/laˈtino/] 拉丁美洲人；拉丁裔的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1981" s="1" t="inlineStr">
@@ -63561,7 +63805,7 @@
       </c>
       <c r="D1981" s="1" t="inlineStr">
         <is>
-          <t>拉丁语</t>
+          <t>拉丁美洲人；拉丁裔的</t>
         </is>
       </c>
       <c r="E1981" s="1" t="inlineStr">
@@ -63743,7 +63987,7 @@
       </c>
       <c r="B1987" s="1" t="inlineStr">
         <is>
-          <t>[ˈantɾo] 书房&lt;名&gt;</t>
+          <t>[/ˈantɾo/] 洞穴；巢穴；藏污纳垢的场所&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1987" s="1" t="inlineStr">
@@ -63753,7 +63997,7 @@
       </c>
       <c r="D1987" s="1" t="inlineStr">
         <is>
-          <t>书房</t>
+          <t>洞穴；巢穴；藏污纳垢的场所</t>
         </is>
       </c>
       <c r="E1987" s="1" t="inlineStr">
@@ -63775,7 +64019,7 @@
       </c>
       <c r="B1988" s="1" t="inlineStr">
         <is>
-          <t>[ˈrae] 雷伊&lt;名&gt;</t>
+          <t>[/ˈrae/] 西班牙皇家语言学院（RAE）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1988" s="1" t="inlineStr">
@@ -63785,7 +64029,7 @@
       </c>
       <c r="D1988" s="1" t="inlineStr">
         <is>
-          <t>雷伊</t>
+          <t>西班牙皇家语言学院（RAE）</t>
         </is>
       </c>
       <c r="E1988" s="1" t="inlineStr">
@@ -64383,7 +64627,7 @@
       </c>
       <c r="B2007" s="1" t="inlineStr">
         <is>
-          <t>[ˈʝanta] 轮缘&lt;名&gt;</t>
+          <t>[/ˈʝanta/] 轮胎；轮辋&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2007" s="1" t="inlineStr">
@@ -64393,7 +64637,7 @@
       </c>
       <c r="D2007" s="1" t="inlineStr">
         <is>
-          <t>轮缘</t>
+          <t>轮胎；轮辋&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2007" s="1" t="inlineStr">
@@ -64415,7 +64659,7 @@
       </c>
       <c r="B2008" s="1" t="inlineStr">
         <is>
-          <t>[ˈteta] 山雀&lt;名&gt;</t>
+          <t>[/ˈteta/] 乳房；乳头&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2008" s="1" t="inlineStr">
@@ -64425,7 +64669,7 @@
       </c>
       <c r="D2008" s="1" t="inlineStr">
         <is>
-          <t>山雀</t>
+          <t>乳房；乳头</t>
         </is>
       </c>
       <c r="E2008" s="1" t="inlineStr">
@@ -64447,7 +64691,7 @@
       </c>
       <c r="B2009" s="1" t="inlineStr">
         <is>
-          <t>[esˈteɾil] 无菌的&lt;形&gt;</t>
+          <t>[/esˈteɾil/] 不育的；贫瘠的；无菌的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2009" s="1" t="inlineStr">
@@ -64457,7 +64701,7 @@
       </c>
       <c r="D2009" s="1" t="inlineStr">
         <is>
-          <t>无菌的</t>
+          <t>不育的；贫瘠的；无菌的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2009" s="1" t="inlineStr">
@@ -64511,7 +64755,7 @@
       </c>
       <c r="B2011" s="1" t="inlineStr">
         <is>
-          <t>[ˈmu] 亩&lt;名&gt;</t>
+          <t>[/ˈmu/] 亩（中国面积单位）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2011" s="1" t="inlineStr">
@@ -64521,7 +64765,7 @@
       </c>
       <c r="D2011" s="1" t="inlineStr">
         <is>
-          <t>亩</t>
+          <t>亩（中国面积单位）</t>
         </is>
       </c>
       <c r="E2011" s="1" t="inlineStr">
@@ -64639,7 +64883,7 @@
       </c>
       <c r="B2015" s="1" t="inlineStr">
         <is>
-          <t>[imˈbite] 邀请&lt;名&gt;</t>
+          <t>[/imˈbite/] invitar的虚拟式（请柬应为invitación）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2015" s="1" t="inlineStr">
@@ -64649,7 +64893,7 @@
       </c>
       <c r="D2015" s="1" t="inlineStr">
         <is>
-          <t>邀请</t>
+          <t>invitar的虚拟式（请柬应为invitación）</t>
         </is>
       </c>
       <c r="E2015" s="1" t="inlineStr">
@@ -64703,7 +64947,7 @@
       </c>
       <c r="B2017" s="1" t="inlineStr">
         <is>
-          <t>[ˈremo] 划船&lt;名&gt;</t>
+          <t>[/ˈremo/] 船桨；划船&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2017" s="1" t="inlineStr">
@@ -64713,7 +64957,7 @@
       </c>
       <c r="D2017" s="1" t="inlineStr">
         <is>
-          <t>划船</t>
+          <t>船桨；划船</t>
         </is>
       </c>
       <c r="E2017" s="1" t="inlineStr">
@@ -64767,7 +65011,7 @@
       </c>
       <c r="B2019" s="1" t="inlineStr">
         <is>
-          <t>[t͡ʃiˈkito] 小一个&lt;名&gt;</t>
+          <t>[/t͡ʃiˈkito/] 小的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2019" s="1" t="inlineStr">
@@ -64777,7 +65021,7 @@
       </c>
       <c r="D2019" s="1" t="inlineStr">
         <is>
-          <t>小一个</t>
+          <t>小的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2019" s="1" t="inlineStr">
@@ -64831,7 +65075,7 @@
       </c>
       <c r="B2021" s="1" t="inlineStr">
         <is>
-          <t>[apaɾˈkaɾ] 公园&lt;动&gt;</t>
+          <t>[/apaɾˈkaɾ/] 停放（车辆）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2021" s="1" t="inlineStr">
@@ -64841,7 +65085,7 @@
       </c>
       <c r="D2021" s="1" t="inlineStr">
         <is>
-          <t>公园</t>
+          <t>停放（车辆）</t>
         </is>
       </c>
       <c r="E2021" s="1" t="inlineStr">
@@ -65439,7 +65683,7 @@
       </c>
       <c r="B2040" s="1" t="inlineStr">
         <is>
-          <t>[autoˈmatika] 自动&lt;名&gt;</t>
+          <t>[/autoˈmatika/] 自动的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2040" s="1" t="inlineStr">
@@ -65449,7 +65693,7 @@
       </c>
       <c r="D2040" s="1" t="inlineStr">
         <is>
-          <t>自动</t>
+          <t>自动的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2040" s="1" t="inlineStr">
@@ -65727,7 +65971,7 @@
       </c>
       <c r="B2049" s="1" t="inlineStr">
         <is>
-          <t>[baˈθjaɾ] 空的&lt;动&gt;</t>
+          <t>[/baˈθjaɾ/] 倒空；清空&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2049" s="1" t="inlineStr">
@@ -65737,7 +65981,7 @@
       </c>
       <c r="D2049" s="1" t="inlineStr">
         <is>
-          <t>空的</t>
+          <t>倒空；清空</t>
         </is>
       </c>
       <c r="E2049" s="1" t="inlineStr">
@@ -66079,7 +66323,7 @@
       </c>
       <c r="B2060" s="1" t="inlineStr">
         <is>
-          <t>[maduˈɾaɾ] 成熟的&lt;动&gt;</t>
+          <t>[/maduˈɾaɾ/] 成熟；使成熟&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2060" s="1" t="inlineStr">
@@ -66089,7 +66333,7 @@
       </c>
       <c r="D2060" s="1" t="inlineStr">
         <is>
-          <t>成熟的</t>
+          <t>成熟；使成熟</t>
         </is>
       </c>
       <c r="E2060" s="1" t="inlineStr">
@@ -66239,7 +66483,7 @@
       </c>
       <c r="B2065" s="1" t="inlineStr">
         <is>
-          <t>[pɾoˈkuɾa] 尝试&lt;名&gt;</t>
+          <t>[/pɾoˈkuɾa/] 努力&lt;名&gt;；照料&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2065" s="1" t="inlineStr">
@@ -66249,7 +66493,7 @@
       </c>
       <c r="D2065" s="1" t="inlineStr">
         <is>
-          <t>尝试</t>
+          <t>努力&lt;名&gt;；照料&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2065" s="1" t="inlineStr">
@@ -66623,7 +66867,7 @@
       </c>
       <c r="B2077" s="1" t="inlineStr">
         <is>
-          <t>[animaˈdoɾ] 艺人&lt;名&gt;</t>
+          <t>[/animaˈdoɾ/] 动画师；主持人；鼓舞者&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2077" s="1" t="inlineStr">
@@ -66633,7 +66877,7 @@
       </c>
       <c r="D2077" s="1" t="inlineStr">
         <is>
-          <t>艺人</t>
+          <t>动画师；主持人；鼓舞者&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2077" s="1" t="inlineStr">
@@ -66943,7 +67187,7 @@
       </c>
       <c r="B2087" s="1" t="inlineStr">
         <is>
-          <t>[simuˈlakɾo] 钻&lt;名&gt;</t>
+          <t>[/simuˈlakɾo/] 演习；模拟；彩排&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2087" s="1" t="inlineStr">
@@ -66953,7 +67197,7 @@
       </c>
       <c r="D2087" s="1" t="inlineStr">
         <is>
-          <t>钻</t>
+          <t>演习；模拟；彩排</t>
         </is>
       </c>
       <c r="E2087" s="1" t="inlineStr">
@@ -67391,7 +67635,7 @@
       </c>
       <c r="B2101" s="1" t="inlineStr">
         <is>
-          <t>[sobɾeˈtodo] 最重要的是&lt;名&gt;</t>
+          <t>[/sobɾeˈtodo/] 大衣；外套&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2101" s="1" t="inlineStr">
@@ -67401,7 +67645,7 @@
       </c>
       <c r="D2101" s="1" t="inlineStr">
         <is>
-          <t>最重要的是</t>
+          <t>大衣；外套</t>
         </is>
       </c>
       <c r="E2101" s="1" t="inlineStr">
@@ -67423,7 +67667,7 @@
       </c>
       <c r="B2102" s="1" t="inlineStr">
         <is>
-          <t>[bomˈbon] 辣妹&lt;名&gt;</t>
+          <t>[/bomˈbon/] 巧克力；（口）俊男/美女&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2102" s="1" t="inlineStr">
@@ -67433,7 +67677,7 @@
       </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
-          <t>辣妹</t>
+          <t>巧克力；（口）俊男/美女</t>
         </is>
       </c>
       <c r="E2102" s="1" t="inlineStr">
@@ -68959,7 +69203,7 @@
       </c>
       <c r="B2150" s="1" t="inlineStr">
         <is>
-          <t>[ˈkiθjo] 鹅毛笔&lt;名&gt;</t>
+          <t>[/ˈkiθjo/] 门框；门轴&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2150" s="1" t="inlineStr">
@@ -68969,7 +69213,7 @@
       </c>
       <c r="D2150" s="1" t="inlineStr">
         <is>
-          <t>鹅毛笔</t>
+          <t>门框；门轴</t>
         </is>
       </c>
       <c r="E2150" s="1" t="inlineStr">
@@ -69599,7 +69843,7 @@
       </c>
       <c r="B2170" s="1" t="inlineStr">
         <is>
-          <t>[kolˈmiʝo] 方&lt;名&gt;</t>
+          <t>[/kolˈmiʝo/] 犬牙；獠牙&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2170" s="1" t="inlineStr">
@@ -69609,7 +69853,7 @@
       </c>
       <c r="D2170" s="1" t="inlineStr">
         <is>
-          <t>方</t>
+          <t>犬牙；獠牙</t>
         </is>
       </c>
       <c r="E2170" s="1" t="inlineStr">
@@ -70047,7 +70291,7 @@
       </c>
       <c r="B2184" s="1" t="inlineStr">
         <is>
-          <t>[memoˈɾjal] 纪念馆&lt;名&gt;</t>
+          <t>[/memoˈɾjal/] 请愿书；陈述书&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2184" s="1" t="inlineStr">
@@ -70057,7 +70301,7 @@
       </c>
       <c r="D2184" s="1" t="inlineStr">
         <is>
-          <t>纪念馆</t>
+          <t>请愿书；陈述书&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2184" s="1" t="inlineStr">
@@ -70271,7 +70515,7 @@
       </c>
       <c r="B2191" s="1" t="inlineStr">
         <is>
-          <t>[ˈpetɾa] 佩特拉&lt;名&gt;</t>
+          <t>[/ˈpetɾa/] 佩特拉&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2191" s="1" t="inlineStr">
@@ -70303,7 +70547,7 @@
       </c>
       <c r="B2192" s="1" t="inlineStr">
         <is>
-          <t>[ˈrin] 莱茵河&lt;名&gt;</t>
+          <t>[/ˈrin/] 莱茵河&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2192" s="1" t="inlineStr">
@@ -70530,7 +70774,11 @@
           <t>大都会&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2199" s="1" t="inlineStr"/>
+      <c r="C2199" s="1" t="inlineStr">
+        <is>
+          <t>/meˈtɾopolis/</t>
+        </is>
+      </c>
       <c r="D2199" s="1" t="inlineStr">
         <is>
           <t>大都会</t>
@@ -70587,7 +70835,7 @@
       </c>
       <c r="B2201" s="1" t="inlineStr">
         <is>
-          <t>[emiˈsoɾa] 车站&lt;名&gt;</t>
+          <t>[/emiˈsoɾa/] 电台；广播电台&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2201" s="1" t="inlineStr">
@@ -70597,7 +70845,7 @@
       </c>
       <c r="D2201" s="1" t="inlineStr">
         <is>
-          <t>车站</t>
+          <t>电台；广播电台</t>
         </is>
       </c>
       <c r="E2201" s="1" t="inlineStr">
@@ -70747,7 +70995,7 @@
       </c>
       <c r="B2206" s="1" t="inlineStr">
         <is>
-          <t>[ˈfeθ] 菲斯&lt;名&gt;</t>
+          <t>[/ˈfeθ/] 菲斯帽&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2206" s="1" t="inlineStr">
@@ -70757,7 +71005,7 @@
       </c>
       <c r="D2206" s="1" t="inlineStr">
         <is>
-          <t>菲斯</t>
+          <t>菲斯帽&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2206" s="1" t="inlineStr">
@@ -70782,7 +71030,11 @@
           <t>阿拉伯&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C2207" s="1" t="inlineStr"/>
+      <c r="C2207" s="1" t="inlineStr">
+        <is>
+          <t>/aɾabˈio/</t>
+        </is>
+      </c>
       <c r="D2207" s="1" t="inlineStr">
         <is>
           <t>阿拉伯</t>
@@ -70871,7 +71123,7 @@
       </c>
       <c r="B2210" s="1" t="inlineStr">
         <is>
-          <t>[ˈpint͡ʃe] 捏&lt;名&gt;</t>
+          <t>[/ˈpint͡ʃe/] 厨房帮工；（墨西哥俚语）该死的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2210" s="1" t="inlineStr">
@@ -70881,7 +71133,7 @@
       </c>
       <c r="D2210" s="1" t="inlineStr">
         <is>
-          <t>捏</t>
+          <t>厨房帮工；（墨西哥俚语）该死的</t>
         </is>
       </c>
       <c r="E2210" s="1" t="inlineStr">
@@ -71127,7 +71379,7 @@
       </c>
       <c r="B2218" s="1" t="inlineStr">
         <is>
-          <t>[deˈset͡ʃo] 未完成的&lt;形&gt;</t>
+          <t>[/deˈset͡ʃo/] 拆散的；解开的；融化的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2218" s="1" t="inlineStr">
@@ -71137,7 +71389,7 @@
       </c>
       <c r="D2218" s="1" t="inlineStr">
         <is>
-          <t>未完成的</t>
+          <t>拆散的；解开的；融化的</t>
         </is>
       </c>
       <c r="E2218" s="1" t="inlineStr">
@@ -71223,7 +71475,7 @@
       </c>
       <c r="B2221" s="1" t="inlineStr">
         <is>
-          <t>[ˈw̝eɾto] 果园&lt;名&gt;</t>
+          <t>[/ˈw̝eɾto/] 菜园&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2221" s="1" t="inlineStr">
@@ -71233,7 +71485,7 @@
       </c>
       <c r="D2221" s="1" t="inlineStr">
         <is>
-          <t>果园</t>
+          <t>菜园&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2221" s="1" t="inlineStr">
@@ -71383,7 +71635,7 @@
       </c>
       <c r="B2226" s="1" t="inlineStr">
         <is>
-          <t>[funˈdido] 演员表&lt;形&gt;</t>
+          <t>[/funˈdido/] 熔化的；熔合的；破产的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2226" s="1" t="inlineStr">
@@ -71393,7 +71645,7 @@
       </c>
       <c r="D2226" s="1" t="inlineStr">
         <is>
-          <t>演员表</t>
+          <t>熔化的；熔合的；破产的</t>
         </is>
       </c>
       <c r="E2226" s="1" t="inlineStr">
@@ -71415,7 +71667,7 @@
       </c>
       <c r="B2227" s="1" t="inlineStr">
         <is>
-          <t>[θiˈtaɾ] 报价&lt;动&gt;</t>
+          <t>[/θiˈtaɾ/] 引用；约定；传唤&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2227" s="1" t="inlineStr">
@@ -71425,7 +71677,7 @@
       </c>
       <c r="D2227" s="1" t="inlineStr">
         <is>
-          <t>报价</t>
+          <t>引用；约定；传唤</t>
         </is>
       </c>
       <c r="E2227" s="1" t="inlineStr">
@@ -71479,7 +71731,7 @@
       </c>
       <c r="B2229" s="1" t="inlineStr">
         <is>
-          <t>[ˈbu] 卜&lt;叹&gt;</t>
+          <t>[/ˈbu/] 呜；嘘（吓人声）&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C2229" s="1" t="inlineStr">
@@ -71489,7 +71741,7 @@
       </c>
       <c r="D2229" s="1" t="inlineStr">
         <is>
-          <t>卜</t>
+          <t>呜；嘘（吓人声）</t>
         </is>
       </c>
       <c r="E2229" s="1" t="inlineStr">
@@ -71543,7 +71795,7 @@
       </c>
       <c r="B2231" s="1" t="inlineStr">
         <is>
-          <t>[pɾenˈdeɾ] 打开&lt;动&gt;</t>
+          <t>[/pɾenˈdeɾ/] 点燃；逮捕；开启（拉美）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2231" s="1" t="inlineStr">
@@ -71553,7 +71805,7 @@
       </c>
       <c r="D2231" s="1" t="inlineStr">
         <is>
-          <t>打开</t>
+          <t>点燃；逮捕；开启（拉美）</t>
         </is>
       </c>
       <c r="E2231" s="1" t="inlineStr">
@@ -72439,7 +72691,7 @@
       </c>
       <c r="B2259" s="1" t="inlineStr">
         <is>
-          <t>[delikaˈdeθa] 美味佳肴&lt;名&gt;</t>
+          <t>[/delikaˈdeθa/] 精致；温柔；体贴&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2259" s="1" t="inlineStr">
@@ -72449,7 +72701,7 @@
       </c>
       <c r="D2259" s="1" t="inlineStr">
         <is>
-          <t>美味佳肴</t>
+          <t>精致；温柔；体贴</t>
         </is>
       </c>
       <c r="E2259" s="1" t="inlineStr">
@@ -72503,7 +72755,7 @@
       </c>
       <c r="B2261" s="1" t="inlineStr">
         <is>
-          <t>[ɡaˈlan] 英勇的&lt;名&gt;</t>
+          <t>[/ɡaˈlan/] 美男子；男主角；求爱者&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2261" s="1" t="inlineStr">
@@ -72513,7 +72765,7 @@
       </c>
       <c r="D2261" s="1" t="inlineStr">
         <is>
-          <t>英勇的</t>
+          <t>美男子；男主角；求爱者</t>
         </is>
       </c>
       <c r="E2261" s="1" t="inlineStr">
@@ -73047,7 +73299,7 @@
       </c>
       <c r="B2278" s="1" t="inlineStr">
         <is>
-          <t>[ˈkexo] 抱怨&lt;名&gt;</t>
+          <t>[/ˈkexo/] queja（抱怨&lt;名&gt;）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2278" s="1" t="inlineStr">
@@ -73057,7 +73309,7 @@
       </c>
       <c r="D2278" s="1" t="inlineStr">
         <is>
-          <t>抱怨</t>
+          <t>queja（抱怨&lt;名&gt;）</t>
         </is>
       </c>
       <c r="E2278" s="1" t="inlineStr">
@@ -73338,7 +73590,11 @@
           <t>融资&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2287" s="1" t="inlineStr"/>
+      <c r="C2287" s="1" t="inlineStr">
+        <is>
+          <t>/finansjaˈsjon/</t>
+        </is>
+      </c>
       <c r="D2287" s="1" t="inlineStr">
         <is>
           <t>融资</t>
@@ -73430,7 +73686,11 @@
           <t>巴拿马&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2290" s="1" t="inlineStr"/>
+      <c r="C2290" s="1" t="inlineStr">
+        <is>
+          <t>/panaˈma/</t>
+        </is>
+      </c>
       <c r="D2290" s="1" t="inlineStr">
         <is>
           <t>巴拿马</t>
@@ -73999,13 +74259,17 @@
       </c>
       <c r="B2308" s="1" t="inlineStr">
         <is>
-          <t>跑&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2308" s="1" t="inlineStr"/>
+          <t>[[ˈran] 跑；奔跑；跑步&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2308" s="1" t="inlineStr">
+        <is>
+          <t>/ɾˈun/</t>
+        </is>
+      </c>
       <c r="D2308" s="1" t="inlineStr">
         <is>
-          <t>跑</t>
+          <t>跑；奔跑；跑步</t>
         </is>
       </c>
       <c r="E2308" s="1" t="inlineStr">
@@ -74091,7 +74355,7 @@
       </c>
       <c r="B2311" s="1" t="inlineStr">
         <is>
-          <t>[tumˈbado] 说谎&lt;形&gt;</t>
+          <t>[/tumˈbado/] 躺着的；平躺&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2311" s="1" t="inlineStr">
@@ -74101,7 +74365,7 @@
       </c>
       <c r="D2311" s="1" t="inlineStr">
         <is>
-          <t>说谎</t>
+          <t>躺着的；平躺</t>
         </is>
       </c>
       <c r="E2311" s="1" t="inlineStr">
@@ -74318,7 +74582,11 @@
           <t>王子&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2318" s="1" t="inlineStr"/>
+      <c r="C2318" s="1" t="inlineStr">
+        <is>
+          <t>/pɾinθˈipe/</t>
+        </is>
+      </c>
       <c r="D2318" s="1" t="inlineStr">
         <is>
           <t>王子</t>
@@ -74343,7 +74611,7 @@
       </c>
       <c r="B2319" s="1" t="inlineStr">
         <is>
-          <t>[ˈfosfoɾo] 比赛&lt;名&gt;</t>
+          <t>[/ˈfosfoɾo/] 火柴；磷&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2319" s="1" t="inlineStr">
@@ -74353,7 +74621,7 @@
       </c>
       <c r="D2319" s="1" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>火柴；磷</t>
         </is>
       </c>
       <c r="E2319" s="1" t="inlineStr">
@@ -74471,7 +74739,7 @@
       </c>
       <c r="B2323" s="1" t="inlineStr">
         <is>
-          <t>[ˈkapa] 河童&lt;名&gt;</t>
+          <t>[/ˈkapa/] 希腊字母 κ&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2323" s="1" t="inlineStr">
@@ -74481,7 +74749,7 @@
       </c>
       <c r="D2323" s="1" t="inlineStr">
         <is>
-          <t>河童</t>
+          <t>希腊字母 κ&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2323" s="1" t="inlineStr">
@@ -74631,7 +74899,7 @@
       </c>
       <c r="B2328" s="1" t="inlineStr">
         <is>
-          <t>[ˈdaɾsela] 给他&lt;动&gt;</t>
+          <t>[/ˈdaɾsela/] 欺骗&lt;动&gt;（dar gato por liebre；常用语 dársela a alguien）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2328" s="1" t="inlineStr">
@@ -74641,7 +74909,7 @@
       </c>
       <c r="D2328" s="1" t="inlineStr">
         <is>
-          <t>给他</t>
+          <t>欺骗&lt;动&gt;（dar gato por liebre；常用语 dársela a alguien）</t>
         </is>
       </c>
       <c r="E2328" s="1" t="inlineStr">
@@ -74663,13 +74931,17 @@
       </c>
       <c r="B2329" s="1" t="inlineStr">
         <is>
-          <t>页面&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2329" s="1" t="inlineStr"/>
+          <t>[[ˈpaχe]] （英语借词）页面&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2329" s="1" t="inlineStr">
+        <is>
+          <t>/pˈaxe/</t>
+        </is>
+      </c>
       <c r="D2329" s="1" t="inlineStr">
         <is>
-          <t>页面</t>
+          <t>（英语借词）页面&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2329" s="1" t="inlineStr">
@@ -74691,7 +74963,7 @@
       </c>
       <c r="B2330" s="1" t="inlineStr">
         <is>
-          <t>[pɾesenˈθjaɾ] 证人&lt;动&gt;</t>
+          <t>[/pɾesenˈθjaɾ/] 目睹；在场见证&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2330" s="1" t="inlineStr">
@@ -74701,7 +74973,7 @@
       </c>
       <c r="D2330" s="1" t="inlineStr">
         <is>
-          <t>证人</t>
+          <t>目睹；在场见证</t>
         </is>
       </c>
       <c r="E2330" s="1" t="inlineStr">
@@ -74723,7 +74995,7 @@
       </c>
       <c r="B2331" s="1" t="inlineStr">
         <is>
-          <t>[ˈtao] 道&lt;名&gt;</t>
+          <t>[/ˈtao/] 道&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2331" s="1" t="inlineStr">
@@ -74883,7 +75155,7 @@
       </c>
       <c r="B2336" s="1" t="inlineStr">
         <is>
-          <t>[deskuˈbjeɾta] 发现了&lt;名&gt;</t>
+          <t>[/deskuˈbjeɾta/] 瞭望；值班瞭望&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2336" s="1" t="inlineStr">
@@ -74893,7 +75165,7 @@
       </c>
       <c r="D2336" s="1" t="inlineStr">
         <is>
-          <t>发现了</t>
+          <t>瞭望；值班瞭望&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2336" s="1" t="inlineStr">
@@ -75174,7 +75446,11 @@
           <t>新闻片&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2345" s="1" t="inlineStr"/>
+      <c r="C2345" s="1" t="inlineStr">
+        <is>
+          <t>/notiθjeɾo/</t>
+        </is>
+      </c>
       <c r="D2345" s="1" t="inlineStr">
         <is>
           <t>新闻片</t>
@@ -75234,7 +75510,11 @@
           <t>后卫&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2347" s="1" t="inlineStr"/>
+      <c r="C2347" s="1" t="inlineStr">
+        <is>
+          <t>/retaɣwaɾðja/</t>
+        </is>
+      </c>
       <c r="D2347" s="1" t="inlineStr">
         <is>
           <t>后卫</t>
@@ -75291,7 +75571,7 @@
       </c>
       <c r="B2349" s="1" t="inlineStr">
         <is>
-          <t>[ˈfan] 方&lt;名&gt;</t>
+          <t>[/ˈfan/] 泥；泥浆&lt;名&gt;（应为 fango）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2349" s="1" t="inlineStr">
@@ -75301,7 +75581,7 @@
       </c>
       <c r="D2349" s="1" t="inlineStr">
         <is>
-          <t>方</t>
+          <t>泥；泥浆&lt;名&gt;（应为 fango）</t>
         </is>
       </c>
       <c r="E2349" s="1" t="inlineStr">
@@ -75323,7 +75603,7 @@
       </c>
       <c r="B2350" s="1" t="inlineStr">
         <is>
-          <t>[ˈmosko] 飞&lt;名&gt;</t>
+          <t>[/ˈmosko/] 虻；大蝇&lt;名&gt;（蚊子应为 mosquito）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2350" s="1" t="inlineStr">
@@ -75333,7 +75613,7 @@
       </c>
       <c r="D2350" s="1" t="inlineStr">
         <is>
-          <t>飞</t>
+          <t>虻；大蝇&lt;名&gt;（蚊子应为 mosquito）</t>
         </is>
       </c>
       <c r="E2350" s="1" t="inlineStr">
@@ -75358,7 +75638,11 @@
           <t>招聘&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2351" s="1" t="inlineStr"/>
+      <c r="C2351" s="1" t="inlineStr">
+        <is>
+          <t>/reklutamjento/</t>
+        </is>
+      </c>
       <c r="D2351" s="1" t="inlineStr">
         <is>
           <t>招聘</t>
@@ -75383,7 +75667,7 @@
       </c>
       <c r="B2352" s="1" t="inlineStr">
         <is>
-          <t>[toˈaɾ] 托阿尔&lt;动&gt;</t>
+          <t>[/toˈaɾ/] 触摸&lt;动&gt;（应为 tocar）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2352" s="1" t="inlineStr">
@@ -75393,7 +75677,7 @@
       </c>
       <c r="D2352" s="1" t="inlineStr">
         <is>
-          <t>托阿尔</t>
+          <t>触摸&lt;动&gt;（应为 tocar）</t>
         </is>
       </c>
       <c r="E2352" s="1" t="inlineStr">
@@ -75415,7 +75699,7 @@
       </c>
       <c r="B2353" s="1" t="inlineStr">
         <is>
-          <t>[ˈpje] 脚&lt;名&gt;</t>
+          <t>[/ˈpje/] 脚；足；底部；英尺&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2353" s="1" t="inlineStr">
@@ -75425,7 +75709,7 @@
       </c>
       <c r="D2353" s="1" t="inlineStr">
         <is>
-          <t>脚</t>
+          <t>脚；足；底部；英尺</t>
         </is>
       </c>
       <c r="E2353" s="1" t="inlineStr">
@@ -75706,7 +75990,11 @@
           <t>不明飞行物&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2362" s="1" t="inlineStr"/>
+      <c r="C2362" s="1" t="inlineStr">
+        <is>
+          <t>/ˈobni/</t>
+        </is>
+      </c>
       <c r="D2362" s="1" t="inlineStr">
         <is>
           <t>不明飞行物</t>
@@ -75827,7 +76115,7 @@
       </c>
       <c r="B2366" s="1" t="inlineStr">
         <is>
-          <t>[ˈbenja] 来了&lt;名&gt;</t>
+          <t>[/ˈbenja/] 许可；准许；鞠躬礼&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2366" s="1" t="inlineStr">
@@ -75837,7 +76125,7 @@
       </c>
       <c r="D2366" s="1" t="inlineStr">
         <is>
-          <t>来了</t>
+          <t>许可；准许；鞠躬礼</t>
         </is>
       </c>
       <c r="E2366" s="1" t="inlineStr">
@@ -75891,7 +76179,7 @@
       </c>
       <c r="B2368" s="1" t="inlineStr">
         <is>
-          <t>[sinɡuˈlaɾ] 单数&lt;名&gt;</t>
+          <t>[/sinɡuˈlaɾ/] 单数的；独特的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2368" s="1" t="inlineStr">
@@ -75901,7 +76189,7 @@
       </c>
       <c r="D2368" s="1" t="inlineStr">
         <is>
-          <t>单数</t>
+          <t>单数的；独特的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2368" s="1" t="inlineStr">
@@ -76214,7 +76502,11 @@
           <t>修指甲&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2378" s="1" t="inlineStr"/>
+      <c r="C2378" s="1" t="inlineStr">
+        <is>
+          <t>/maniˈkuɾo/</t>
+        </is>
+      </c>
       <c r="D2378" s="1" t="inlineStr">
         <is>
           <t>修指甲</t>
@@ -76399,7 +76691,7 @@
       </c>
       <c r="B2384" s="1" t="inlineStr">
         <is>
-          <t>[ˈmaɾi] 马里&lt;名&gt;</t>
+          <t>[/ˈmaɾi/] （口语）朋友；哥们&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2384" s="1" t="inlineStr">
@@ -76409,7 +76701,7 @@
       </c>
       <c r="D2384" s="1" t="inlineStr">
         <is>
-          <t>马里</t>
+          <t>（口语）朋友；哥们</t>
         </is>
       </c>
       <c r="E2384" s="1" t="inlineStr">
@@ -76943,7 +77235,7 @@
       </c>
       <c r="B2401" s="1" t="inlineStr">
         <is>
-          <t>[reˈpleto] 包装好的&lt;形&gt;</t>
+          <t>[/reˈpleto/] 充满的；装满的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2401" s="1" t="inlineStr">
@@ -76953,7 +77245,7 @@
       </c>
       <c r="D2401" s="1" t="inlineStr">
         <is>
-          <t>包装好的</t>
+          <t>充满的；装满的</t>
         </is>
       </c>
       <c r="E2401" s="1" t="inlineStr">
@@ -77618,7 +77910,11 @@
           <t>房地产&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2422" s="1" t="inlineStr"/>
+      <c r="C2422" s="1" t="inlineStr">
+        <is>
+          <t>/inmoβiˈljaɾja/</t>
+        </is>
+      </c>
       <c r="D2422" s="1" t="inlineStr">
         <is>
           <t>房地产</t>
@@ -77803,7 +78099,7 @@
       </c>
       <c r="B2428" s="1" t="inlineStr">
         <is>
-          <t>[lideˈɾaɾ] 铅&lt;动&gt;</t>
+          <t>[/lideˈɾaɾ/] 领导；带领；位居首位&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2428" s="1" t="inlineStr">
@@ -77813,7 +78109,7 @@
       </c>
       <c r="D2428" s="1" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>领导；带领；位居首位</t>
         </is>
       </c>
       <c r="E2428" s="1" t="inlineStr">
@@ -77963,7 +78259,7 @@
       </c>
       <c r="B2433" s="1" t="inlineStr">
         <is>
-          <t>[ˈbalido] 有效&lt;形&gt;</t>
+          <t>[/ˈbalido/] 有效的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2433" s="1" t="inlineStr">
@@ -77973,7 +78269,7 @@
       </c>
       <c r="D2433" s="1" t="inlineStr">
         <is>
-          <t>有效</t>
+          <t>有效的</t>
         </is>
       </c>
       <c r="E2433" s="1" t="inlineStr">
@@ -78126,7 +78422,11 @@
           <t>厚&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2438" s="1" t="inlineStr"/>
+      <c r="C2438" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɡɾesa/</t>
+        </is>
+      </c>
       <c r="D2438" s="1" t="inlineStr">
         <is>
           <t>厚</t>
@@ -78311,7 +78611,7 @@
       </c>
       <c r="B2444" s="1" t="inlineStr">
         <is>
-          <t>[pɾokuɾaˈdoɾ] 律师&lt;名&gt;</t>
+          <t>[/pɾokuɾaˈdoɾ/] 诉讼代理人；受权人（西班牙司法体系中代表当事人在法院行事者，非律师 abogado）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2444" s="1" t="inlineStr">
@@ -78321,7 +78621,7 @@
       </c>
       <c r="D2444" s="1" t="inlineStr">
         <is>
-          <t>律师</t>
+          <t>诉讼代理人；受权人（西班牙司法体系中代表当事人在法院行事者，非律师 abogado）</t>
         </is>
       </c>
       <c r="E2444" s="1" t="inlineStr">
@@ -78343,7 +78643,7 @@
       </c>
       <c r="B2445" s="1" t="inlineStr">
         <is>
-          <t>[deliˈɾaɾ] 狂欢&lt;动&gt;</t>
+          <t>[/deliˈɾaɾ/] 胡言乱语；说呓语；狂热&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2445" s="1" t="inlineStr">
@@ -78353,7 +78653,7 @@
       </c>
       <c r="D2445" s="1" t="inlineStr">
         <is>
-          <t>狂欢</t>
+          <t>胡言乱语；说呓语；狂热</t>
         </is>
       </c>
       <c r="E2445" s="1" t="inlineStr">
@@ -78631,7 +78931,7 @@
       </c>
       <c r="B2454" s="1" t="inlineStr">
         <is>
-          <t>[blinˈdado] 装甲的&lt;名&gt;</t>
+          <t>[/blinˈdado/] 装甲的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2454" s="1" t="inlineStr">
@@ -78641,7 +78941,7 @@
       </c>
       <c r="D2454" s="1" t="inlineStr">
         <is>
-          <t>装甲的</t>
+          <t>装甲的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2454" s="1" t="inlineStr">
@@ -78695,7 +78995,7 @@
       </c>
       <c r="B2456" s="1" t="inlineStr">
         <is>
-          <t>[ˈkate] 美食&lt;名&gt;</t>
+          <t>[/ˈkate/] 不及格；失败；毒打（口语）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2456" s="1" t="inlineStr">
@@ -78705,7 +79005,7 @@
       </c>
       <c r="D2456" s="1" t="inlineStr">
         <is>
-          <t>美食</t>
+          <t>不及格；失败；毒打（口语）</t>
         </is>
       </c>
       <c r="E2456" s="1" t="inlineStr">
@@ -78887,7 +79187,7 @@
       </c>
       <c r="B2462" s="1" t="inlineStr">
         <is>
-          <t>[ˈonda] 本田&lt;名&gt;</t>
+          <t>[/ˈonda/] 深的；深沉的；投石器&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2462" s="1" t="inlineStr">
@@ -78897,7 +79197,7 @@
       </c>
       <c r="D2462" s="1" t="inlineStr">
         <is>
-          <t>本田</t>
+          <t>深的；深沉的；投石器</t>
         </is>
       </c>
       <c r="E2462" s="1" t="inlineStr">
@@ -79047,7 +79347,7 @@
       </c>
       <c r="B2467" s="1" t="inlineStr">
         <is>
-          <t>[nubˈθjal] 新娘&lt;形&gt;</t>
+          <t>[/nubˈθjal/] 婚礼的；婚姻的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2467" s="1" t="inlineStr">
@@ -79057,7 +79357,7 @@
       </c>
       <c r="D2467" s="1" t="inlineStr">
         <is>
-          <t>新娘</t>
+          <t>婚礼的；婚姻的</t>
         </is>
       </c>
       <c r="E2467" s="1" t="inlineStr">
@@ -79143,13 +79443,17 @@
       </c>
       <c r="B2470" s="1" t="inlineStr">
         <is>
-          <t>我们游行&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2470" s="1" t="inlineStr"/>
+          <t>[[maɾˈtʃamo] 印章；封印；标记；品质标志&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2470" s="1" t="inlineStr">
+        <is>
+          <t>/maɾˈt͡ʃamo/</t>
+        </is>
+      </c>
       <c r="D2470" s="1" t="inlineStr">
         <is>
-          <t>我们游行</t>
+          <t>印章；封印；标记；品质标志</t>
         </is>
       </c>
       <c r="E2470" s="1" t="inlineStr">
@@ -79747,7 +80051,7 @@
       </c>
       <c r="B2489" s="1" t="inlineStr">
         <is>
-          <t>[ˈibɾido] 混合动力&lt;名&gt;</t>
+          <t>[/ˈibɾido/] 杂交的，混合的&lt;形&gt;；杂交种，混合物&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2489" s="1" t="inlineStr">
@@ -79757,7 +80061,7 @@
       </c>
       <c r="D2489" s="1" t="inlineStr">
         <is>
-          <t>混合动力</t>
+          <t>杂交的，混合的&lt;形&gt;；杂交种，混合物&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2489" s="1" t="inlineStr">
@@ -79814,7 +80118,11 @@
           <t>游戏&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2491" s="1" t="inlineStr"/>
+      <c r="C2491" s="1" t="inlineStr">
+        <is>
+          <t>/ɡˈame/</t>
+        </is>
+      </c>
       <c r="D2491" s="1" t="inlineStr">
         <is>
           <t>游戏</t>
@@ -80514,7 +80822,11 @@
           <t>同性恋者&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C2513" s="1" t="inlineStr"/>
+      <c r="C2513" s="1" t="inlineStr">
+        <is>
+          <t>/ˈomo/</t>
+        </is>
+      </c>
       <c r="D2513" s="1" t="inlineStr">
         <is>
           <t>同性恋者</t>
@@ -80830,7 +81142,11 @@
           <t>查尔斯顿&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2523" s="1" t="inlineStr"/>
+      <c r="C2523" s="1" t="inlineStr">
+        <is>
+          <t>/tʃaɾlˈeston/</t>
+        </is>
+      </c>
       <c r="D2523" s="1" t="inlineStr">
         <is>
           <t>查尔斯顿</t>
@@ -81047,7 +81363,7 @@
       </c>
       <c r="B2530" s="1" t="inlineStr">
         <is>
-          <t>[ˈostjas] 主机&lt;叹&gt;</t>
+          <t>[/ˈostjas/] 该死！；见鬼！（粗俗感叹词）；圣饼&lt;intj&gt;</t>
         </is>
       </c>
       <c r="C2530" s="1" t="inlineStr">
@@ -81057,7 +81373,7 @@
       </c>
       <c r="D2530" s="1" t="inlineStr">
         <is>
-          <t>主机</t>
+          <t>该死！；见鬼！（粗俗感叹词）；圣饼</t>
         </is>
       </c>
       <c r="E2530" s="1" t="inlineStr">
@@ -81079,7 +81395,7 @@
       </c>
       <c r="B2531" s="1" t="inlineStr">
         <is>
-          <t>[auˈɡusto] 八月&lt;形&gt;</t>
+          <t>[/auˈɡusto/] 威严的；庄严的；尊贵的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2531" s="1" t="inlineStr">
@@ -81089,7 +81405,7 @@
       </c>
       <c r="D2531" s="1" t="inlineStr">
         <is>
-          <t>八月</t>
+          <t>威严的；庄严的；尊贵的</t>
         </is>
       </c>
       <c r="E2531" s="1" t="inlineStr">
@@ -81239,7 +81555,7 @@
       </c>
       <c r="B2536" s="1" t="inlineStr">
         <is>
-          <t>[ˈmoo] 模具&lt;名&gt;</t>
+          <t>[/ˈmoo/] 霉；霉菌；锈斑&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2536" s="1" t="inlineStr">
@@ -81249,7 +81565,7 @@
       </c>
       <c r="D2536" s="1" t="inlineStr">
         <is>
-          <t>模具</t>
+          <t>霉；霉菌；锈斑</t>
         </is>
       </c>
       <c r="E2536" s="1" t="inlineStr">
@@ -81495,7 +81811,7 @@
       </c>
       <c r="B2544" s="1" t="inlineStr">
         <is>
-          <t>[filtɾaˈθjon] 过滤&lt;名&gt;</t>
+          <t>[/filtɾaˈθjon/] 泄漏，泄露；过滤&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2544" s="1" t="inlineStr">
@@ -81505,7 +81821,7 @@
       </c>
       <c r="D2544" s="1" t="inlineStr">
         <is>
-          <t>过滤</t>
+          <t>泄漏，泄露；过滤</t>
         </is>
       </c>
       <c r="E2544" s="1" t="inlineStr">
@@ -81530,7 +81846,11 @@
           <t>土地&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2545" s="1" t="inlineStr"/>
+      <c r="C2545" s="1" t="inlineStr">
+        <is>
+          <t>/lˈand/</t>
+        </is>
+      </c>
       <c r="D2545" s="1" t="inlineStr">
         <is>
           <t>土地</t>
@@ -81683,13 +82003,17 @@
       </c>
       <c r="B2550" s="1" t="inlineStr">
         <is>
-          <t>玛丽安&lt;形&gt;</t>
-        </is>
-      </c>
-      <c r="C2550" s="1" t="inlineStr"/>
+          <t>[[maˈɾja.no] 圣母玛利亚的；圣母的&lt;adj&gt;</t>
+        </is>
+      </c>
+      <c r="C2550" s="1" t="inlineStr">
+        <is>
+          <t>/maˈɾjano/</t>
+        </is>
+      </c>
       <c r="D2550" s="1" t="inlineStr">
         <is>
-          <t>玛丽安</t>
+          <t>圣母玛利亚的；圣母的</t>
         </is>
       </c>
       <c r="E2550" s="1" t="inlineStr">
@@ -81743,7 +82067,7 @@
       </c>
       <c r="B2552" s="1" t="inlineStr">
         <is>
-          <t>[duɾˈmjente] 卧铺&lt;名&gt;</t>
+          <t>[/duɾˈmjente/] 睡着的人；枕木&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2552" s="1" t="inlineStr">
@@ -81753,7 +82077,7 @@
       </c>
       <c r="D2552" s="1" t="inlineStr">
         <is>
-          <t>卧铺</t>
+          <t>睡着的人；枕木</t>
         </is>
       </c>
       <c r="E2552" s="1" t="inlineStr">
@@ -82255,7 +82579,7 @@
       </c>
       <c r="B2568" s="1" t="inlineStr">
         <is>
-          <t>[sentenˈθjaɾ] 句子&lt;动&gt;</t>
+          <t>[/sentenˈθjaɾ/] 判决；宣判；断言&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2568" s="1" t="inlineStr">
@@ -82265,7 +82589,7 @@
       </c>
       <c r="D2568" s="1" t="inlineStr">
         <is>
-          <t>句子</t>
+          <t>判决；宣判；断言</t>
         </is>
       </c>
       <c r="E2568" s="1" t="inlineStr">
@@ -82418,7 +82742,11 @@
           <t>西方的&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2573" s="1" t="inlineStr"/>
+      <c r="C2573" s="1" t="inlineStr">
+        <is>
+          <t>/wˈesteɾn/</t>
+        </is>
+      </c>
       <c r="D2573" s="1" t="inlineStr">
         <is>
           <t>西方的</t>
@@ -82507,7 +82835,7 @@
       </c>
       <c r="B2576" s="1" t="inlineStr">
         <is>
-          <t>[ɡɾaˈdwaɾ] 毕业生&lt;动&gt;</t>
+          <t>[/ɡɾaˈdwaɾ/] 分级；标定；校准；使毕业&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2576" s="1" t="inlineStr">
@@ -82517,7 +82845,7 @@
       </c>
       <c r="D2576" s="1" t="inlineStr">
         <is>
-          <t>毕业生</t>
+          <t>分级；标定；校准；使毕业</t>
         </is>
       </c>
       <c r="E2576" s="1" t="inlineStr">
@@ -83051,7 +83379,7 @@
       </c>
       <c r="B2593" s="1" t="inlineStr">
         <is>
-          <t>[ˈoseo] 骨头&lt;形&gt;</t>
+          <t>[/ˈoseo/] 骨的；骨骼的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2593" s="1" t="inlineStr">
@@ -83061,7 +83389,7 @@
       </c>
       <c r="D2593" s="1" t="inlineStr">
         <is>
-          <t>骨头</t>
+          <t>骨的；骨骼的</t>
         </is>
       </c>
       <c r="E2593" s="1" t="inlineStr">
@@ -83083,7 +83411,7 @@
       </c>
       <c r="B2594" s="1" t="inlineStr">
         <is>
-          <t>[ˈka] 卡&lt;名&gt;</t>
+          <t>[/ˈka/] 字母K&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2594" s="1" t="inlineStr">
@@ -83093,7 +83421,7 @@
       </c>
       <c r="D2594" s="1" t="inlineStr">
         <is>
-          <t>卡</t>
+          <t>字母K</t>
         </is>
       </c>
       <c r="E2594" s="1" t="inlineStr">
@@ -83307,7 +83635,7 @@
       </c>
       <c r="B2601" s="1" t="inlineStr">
         <is>
-          <t>[kompɾomeˈteɾ] 提交&lt;动&gt;</t>
+          <t>[/kompɾomeˈteɾ/] 承诺；使承担义务；危及；连累&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2601" s="1" t="inlineStr">
@@ -83317,7 +83645,7 @@
       </c>
       <c r="D2601" s="1" t="inlineStr">
         <is>
-          <t>提交</t>
+          <t>承诺；使承担义务；危及；连累</t>
         </is>
       </c>
       <c r="E2601" s="1" t="inlineStr">
@@ -84206,7 +84534,11 @@
           <t>遗憾&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C2629" s="1" t="inlineStr"/>
+      <c r="C2629" s="1" t="inlineStr">
+        <is>
+          <t>/arepenˈtiɾ/</t>
+        </is>
+      </c>
       <c r="D2629" s="1" t="inlineStr">
         <is>
           <t>遗憾</t>
@@ -84359,7 +84691,7 @@
       </c>
       <c r="B2634" s="1" t="inlineStr">
         <is>
-          <t>[t͡ʃuˈleta] 砍&lt;名&gt;</t>
+          <t>[/t͡ʃuˈleta/] 猪排；肉排&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2634" s="1" t="inlineStr">
@@ -84369,7 +84701,7 @@
       </c>
       <c r="D2634" s="1" t="inlineStr">
         <is>
-          <t>砍</t>
+          <t>猪排；肉排</t>
         </is>
       </c>
       <c r="E2634" s="1" t="inlineStr">
@@ -84711,7 +85043,7 @@
       </c>
       <c r="B2645" s="1" t="inlineStr">
         <is>
-          <t>[ˈswin] 秋千&lt;名&gt;</t>
+          <t>[/ˈswin/] 摇摆乐；摇摆舞&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2645" s="1" t="inlineStr">
@@ -84721,7 +85053,7 @@
       </c>
       <c r="D2645" s="1" t="inlineStr">
         <is>
-          <t>秋千</t>
+          <t>摇摆乐；摇摆舞</t>
         </is>
       </c>
       <c r="E2645" s="1" t="inlineStr">
@@ -85383,7 +85715,7 @@
       </c>
       <c r="B2666" s="1" t="inlineStr">
         <is>
-          <t>[ˈneθjo] 傻瓜&lt;名&gt;</t>
+          <t>[/ˈneθjo/] 愚蠢的&lt;形&gt;；傻瓜&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2666" s="1" t="inlineStr">
@@ -85393,7 +85725,7 @@
       </c>
       <c r="D2666" s="1" t="inlineStr">
         <is>
-          <t>傻瓜</t>
+          <t>愚蠢的&lt;形&gt;；傻瓜&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2666" s="1" t="inlineStr">
@@ -85521,7 +85853,7 @@
       </c>
       <c r="D2670" s="1" t="inlineStr">
         <is>
-          <t>朋友</t>
+          <t>（非西班牙语词，西语应为 amigo）朋友&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2670" s="1" t="inlineStr">
@@ -85546,7 +85878,11 @@
           <t>通常&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C2671" s="1" t="inlineStr"/>
+      <c r="C2671" s="1" t="inlineStr">
+        <is>
+          <t>/aβitwaˈmente/</t>
+        </is>
+      </c>
       <c r="D2671" s="1" t="inlineStr">
         <is>
           <t>通常</t>
@@ -85635,7 +85971,7 @@
       </c>
       <c r="B2674" s="1" t="inlineStr">
         <is>
-          <t>[ˈsubdito] 主题&lt;名&gt;</t>
+          <t>[/ˈsubdito/] 臣民；国民&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2674" s="1" t="inlineStr">
@@ -85645,7 +85981,7 @@
       </c>
       <c r="D2674" s="1" t="inlineStr">
         <is>
-          <t>主题</t>
+          <t>臣民；国民</t>
         </is>
       </c>
       <c r="E2674" s="1" t="inlineStr">
@@ -85827,7 +86163,7 @@
       </c>
       <c r="B2680" s="1" t="inlineStr">
         <is>
-          <t>[peɾˈsjana] 盲人&lt;名&gt;</t>
+          <t>[/peɾˈsjana/] 百叶窗；卷帘&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2680" s="1" t="inlineStr">
@@ -85837,7 +86173,7 @@
       </c>
       <c r="D2680" s="1" t="inlineStr">
         <is>
-          <t>盲人</t>
+          <t>百叶窗；卷帘</t>
         </is>
       </c>
       <c r="E2680" s="1" t="inlineStr">
@@ -85894,7 +86230,11 @@
           <t>化疗&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2682" s="1" t="inlineStr"/>
+      <c r="C2682" s="1" t="inlineStr">
+        <is>
+          <t>/kimiˈo/</t>
+        </is>
+      </c>
       <c r="D2682" s="1" t="inlineStr">
         <is>
           <t>化疗</t>
@@ -86175,7 +86515,7 @@
       </c>
       <c r="B2691" s="1" t="inlineStr">
         <is>
-          <t>[seˈʝaɾ] 密封件&lt;动&gt;</t>
+          <t>[/seˈʝaɾ/] 密封；盖章；封口&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2691" s="1" t="inlineStr">
@@ -86185,7 +86525,7 @@
       </c>
       <c r="D2691" s="1" t="inlineStr">
         <is>
-          <t>密封件</t>
+          <t>密封；盖章；封口</t>
         </is>
       </c>
       <c r="E2691" s="1" t="inlineStr">
@@ -86655,7 +86995,7 @@
       </c>
       <c r="B2706" s="1" t="inlineStr">
         <is>
-          <t>[ˈmoɾo] 沼泽&lt;名&gt;</t>
+          <t>[/ˈmoɾo/] 摩尔人&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2706" s="1" t="inlineStr">
@@ -86665,7 +87005,7 @@
       </c>
       <c r="D2706" s="1" t="inlineStr">
         <is>
-          <t>沼泽</t>
+          <t>摩尔人</t>
         </is>
       </c>
       <c r="E2706" s="1" t="inlineStr">
@@ -86911,7 +87251,7 @@
       </c>
       <c r="B2714" s="1" t="inlineStr">
         <is>
-          <t>[desˈmaʝo] 微弱的&lt;名&gt;</t>
+          <t>[/desˈmaʝo/] 昏厥；昏倒&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2714" s="1" t="inlineStr">
@@ -86921,7 +87261,7 @@
       </c>
       <c r="D2714" s="1" t="inlineStr">
         <is>
-          <t>微弱的</t>
+          <t>昏厥；昏倒</t>
         </is>
       </c>
       <c r="E2714" s="1" t="inlineStr">
@@ -87042,7 +87382,11 @@
           <t>抱怨&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C2718" s="1" t="inlineStr"/>
+      <c r="C2718" s="1" t="inlineStr">
+        <is>
+          <t>/keˈxando/</t>
+        </is>
+      </c>
       <c r="D2718" s="1" t="inlineStr">
         <is>
           <t>抱怨</t>
@@ -87259,7 +87603,7 @@
       </c>
       <c r="B2725" s="1" t="inlineStr">
         <is>
-          <t>[θeˈroxo] 螺栓&lt;名&gt;</t>
+          <t>[/θeˈroxo/] 门闩；插销&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2725" s="1" t="inlineStr">
@@ -87269,7 +87613,7 @@
       </c>
       <c r="D2725" s="1" t="inlineStr">
         <is>
-          <t>螺栓</t>
+          <t>门闩；插销</t>
         </is>
       </c>
       <c r="E2725" s="1" t="inlineStr">
@@ -87739,7 +88083,7 @@
       </c>
       <c r="B2740" s="1" t="inlineStr">
         <is>
-          <t>[reˈlebo] 救济&lt;名&gt;</t>
+          <t>[/reˈlebo/] 接替；换班；接力&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2740" s="1" t="inlineStr">
@@ -87749,7 +88093,7 @@
       </c>
       <c r="D2740" s="1" t="inlineStr">
         <is>
-          <t>救济</t>
+          <t>接替；换班；接力</t>
         </is>
       </c>
       <c r="E2740" s="1" t="inlineStr">
@@ -87774,7 +88118,11 @@
           <t>漫画&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2741" s="1" t="inlineStr"/>
+      <c r="C2741" s="1" t="inlineStr">
+        <is>
+          <t>/komˈiθ/</t>
+        </is>
+      </c>
       <c r="D2741" s="1" t="inlineStr">
         <is>
           <t>漫画</t>
@@ -87863,7 +88211,7 @@
       </c>
       <c r="B2744" s="1" t="inlineStr">
         <is>
-          <t>[pɾoˈdixjo] 神童&lt;名&gt;</t>
+          <t>[/pɾoˈdixjo/] 奇迹；奇才&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2744" s="1" t="inlineStr">
@@ -87873,7 +88221,7 @@
       </c>
       <c r="D2744" s="1" t="inlineStr">
         <is>
-          <t>神童</t>
+          <t>奇迹；奇才&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2744" s="1" t="inlineStr">
@@ -87991,7 +88339,7 @@
       </c>
       <c r="B2748" s="1" t="inlineStr">
         <is>
-          <t>[ˈwa] 佤族&lt;名&gt;</t>
+          <t>[/ˈwa/] 字母W&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2748" s="1" t="inlineStr">
@@ -88001,7 +88349,7 @@
       </c>
       <c r="D2748" s="1" t="inlineStr">
         <is>
-          <t>佤族</t>
+          <t>字母W</t>
         </is>
       </c>
       <c r="E2748" s="1" t="inlineStr">
@@ -88055,7 +88403,7 @@
       </c>
       <c r="B2750" s="1" t="inlineStr">
         <is>
-          <t>[ˈkeme] 烧伤&lt;名&gt;</t>
+          <t>[/ˈkeme/] 烧伤（quemadura 的口语说法）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2750" s="1" t="inlineStr">
@@ -88065,7 +88413,7 @@
       </c>
       <c r="D2750" s="1" t="inlineStr">
         <is>
-          <t>烧伤</t>
+          <t>烧伤（quemadura 的口语说法）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2750" s="1" t="inlineStr">
@@ -88247,7 +88595,7 @@
       </c>
       <c r="B2756" s="1" t="inlineStr">
         <is>
-          <t>[ˈθeɾda] 播种&lt;名&gt;</t>
+          <t>[/ˈθeɾda/] 猪鬃；鬃毛；母猪&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2756" s="1" t="inlineStr">
@@ -88257,7 +88605,7 @@
       </c>
       <c r="D2756" s="1" t="inlineStr">
         <is>
-          <t>播种</t>
+          <t>猪鬃；鬃毛；母猪</t>
         </is>
       </c>
       <c r="E2756" s="1" t="inlineStr">
@@ -88439,7 +88787,7 @@
       </c>
       <c r="B2762" s="1" t="inlineStr">
         <is>
-          <t>[kombaˈtjente] 战斗机&lt;名&gt;</t>
+          <t>[/kombaˈtjente/] 战士；战斗人员&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2762" s="1" t="inlineStr">
@@ -88449,7 +88797,7 @@
       </c>
       <c r="D2762" s="1" t="inlineStr">
         <is>
-          <t>战斗机</t>
+          <t>战士；战斗人员</t>
         </is>
       </c>
       <c r="E2762" s="1" t="inlineStr">
@@ -88730,7 +89078,11 @@
           <t>超级巨星&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2771" s="1" t="inlineStr"/>
+      <c r="C2771" s="1" t="inlineStr">
+        <is>
+          <t>/supeɾestɾˈeʝa/</t>
+        </is>
+      </c>
       <c r="D2771" s="1" t="inlineStr">
         <is>
           <t>超级巨星</t>
@@ -89171,7 +89523,7 @@
       </c>
       <c r="B2785" s="1" t="inlineStr">
         <is>
-          <t>[ˈfalte] 失踪&lt;名&gt;</t>
+          <t>[/ˈfalte/] faltar 缺少&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2785" s="1" t="inlineStr">
@@ -89181,7 +89533,7 @@
       </c>
       <c r="D2785" s="1" t="inlineStr">
         <is>
-          <t>失踪</t>
+          <t>faltar 缺少&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2785" s="1" t="inlineStr">
@@ -89971,7 +90323,7 @@
       </c>
       <c r="B2810" s="1" t="inlineStr">
         <is>
-          <t>[amaɾˈɡado] 苦的&lt;形&gt;</t>
+          <t>[/amaɾˈɡado/] 愤愤不平的，心怀怨恨的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2810" s="1" t="inlineStr">
@@ -89981,7 +90333,7 @@
       </c>
       <c r="D2810" s="1" t="inlineStr">
         <is>
-          <t>苦的</t>
+          <t>愤愤不平的，心怀怨恨的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2810" s="1" t="inlineStr">
@@ -90067,7 +90419,7 @@
       </c>
       <c r="B2813" s="1" t="inlineStr">
         <is>
-          <t>[ˈleu] 亮氨酸&lt;名&gt;</t>
+          <t>[/ˈleu/] 列伊（罗马尼亚货币单位）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2813" s="1" t="inlineStr">
@@ -90077,7 +90429,7 @@
       </c>
       <c r="D2813" s="1" t="inlineStr">
         <is>
-          <t>亮氨酸</t>
+          <t>列伊（罗马尼亚货币单位）</t>
         </is>
       </c>
       <c r="E2813" s="1" t="inlineStr">
@@ -90291,7 +90643,7 @@
       </c>
       <c r="B2820" s="1" t="inlineStr">
         <is>
-          <t>[poɾˈton] 门&lt;名&gt;</t>
+          <t>[/poɾˈton/] 大门&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2820" s="1" t="inlineStr">
@@ -90301,7 +90653,7 @@
       </c>
       <c r="D2820" s="1" t="inlineStr">
         <is>
-          <t>门</t>
+          <t>大门&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2820" s="1" t="inlineStr">
@@ -90355,7 +90707,7 @@
       </c>
       <c r="B2822" s="1" t="inlineStr">
         <is>
-          <t>[rinˈɡaɾ] 林加尔&lt;动&gt;</t>
+          <t>[/rinˈɡaɾ/] 非标准西语词，无此词条&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2822" s="1" t="inlineStr">
@@ -90365,7 +90717,7 @@
       </c>
       <c r="D2822" s="1" t="inlineStr">
         <is>
-          <t>林加尔</t>
+          <t>非标准西语词，无此词条</t>
         </is>
       </c>
       <c r="E2822" s="1" t="inlineStr">
@@ -90870,7 +91222,11 @@
           <t>亿万富翁&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2838" s="1" t="inlineStr"/>
+      <c r="C2838" s="1" t="inlineStr">
+        <is>
+          <t>/multimiʝoˈnaɾjo/</t>
+        </is>
+      </c>
       <c r="D2838" s="1" t="inlineStr">
         <is>
           <t>亿万富翁</t>
@@ -91311,7 +91667,7 @@
       </c>
       <c r="B2852" s="1" t="inlineStr">
         <is>
-          <t>[masaˈxista] 女按摩师&lt;名&gt;</t>
+          <t>[/masaˈxista/] 按摩师&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2852" s="1" t="inlineStr">
@@ -91321,7 +91677,7 @@
       </c>
       <c r="D2852" s="1" t="inlineStr">
         <is>
-          <t>女按摩师</t>
+          <t>按摩师</t>
         </is>
       </c>
       <c r="E2852" s="1" t="inlineStr">
@@ -91535,7 +91891,7 @@
       </c>
       <c r="B2859" s="1" t="inlineStr">
         <is>
-          <t>[retoˈmaɾ] 简历&lt;动&gt;</t>
+          <t>[/retoˈmaɾ/] 恢复；重新开始；取回&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2859" s="1" t="inlineStr">
@@ -91545,7 +91901,7 @@
       </c>
       <c r="D2859" s="1" t="inlineStr">
         <is>
-          <t>简历</t>
+          <t>恢复；重新开始；取回</t>
         </is>
       </c>
       <c r="E2859" s="1" t="inlineStr">
@@ -92047,7 +92403,7 @@
       </c>
       <c r="B2875" s="1" t="inlineStr">
         <is>
-          <t>[ˈʝuki] 由希&lt;名&gt;</t>
+          <t>[/ˈʝuki/] 由希（人名）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2875" s="1" t="inlineStr">
@@ -92057,7 +92413,7 @@
       </c>
       <c r="D2875" s="1" t="inlineStr">
         <is>
-          <t>由希</t>
+          <t>由希（人名）</t>
         </is>
       </c>
       <c r="E2875" s="1" t="inlineStr">
@@ -92274,7 +92630,11 @@
           <t>基本上&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C2882" s="1" t="inlineStr"/>
+      <c r="C2882" s="1" t="inlineStr">
+        <is>
+          <t>/basikamˈente/</t>
+        </is>
+      </c>
       <c r="D2882" s="1" t="inlineStr">
         <is>
           <t>基本上</t>
@@ -92430,7 +92790,11 @@
           <t>名词&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2887" s="1" t="inlineStr"/>
+      <c r="C2887" s="1" t="inlineStr">
+        <is>
+          <t>/ˈnombɾe/</t>
+        </is>
+      </c>
       <c r="D2887" s="1" t="inlineStr">
         <is>
           <t>名词</t>
@@ -92647,7 +93011,7 @@
       </c>
       <c r="B2894" s="1" t="inlineStr">
         <is>
-          <t>[pɾesθinˈdiɾ] 分配&lt;动&gt;</t>
+          <t>[/pɾesθinˈdiɾ/] 省去；不用；摆脱；无视&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2894" s="1" t="inlineStr">
@@ -92657,7 +93021,7 @@
       </c>
       <c r="D2894" s="1" t="inlineStr">
         <is>
-          <t>分配</t>
+          <t>省去；不用；摆脱；无视</t>
         </is>
       </c>
       <c r="E2894" s="1" t="inlineStr">
@@ -92903,7 +93267,7 @@
       </c>
       <c r="B2902" s="1" t="inlineStr">
         <is>
-          <t>[fotoɡɾaˈfjaɾ] 照片&lt;动&gt;</t>
+          <t>[/fotoɡɾaˈfjaɾ/] 拍照；摄影&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2902" s="1" t="inlineStr">
@@ -92913,7 +93277,7 @@
       </c>
       <c r="D2902" s="1" t="inlineStr">
         <is>
-          <t>照片</t>
+          <t>拍照；摄影</t>
         </is>
       </c>
       <c r="E2902" s="1" t="inlineStr">
@@ -92999,13 +93363,17 @@
       </c>
       <c r="B2905" s="1" t="inlineStr">
         <is>
-          <t>讷&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2905" s="1" t="inlineStr"/>
+          <t>[[ˈne]] ni（既不；也不）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2905" s="1" t="inlineStr">
+        <is>
+          <t>/ˈni/</t>
+        </is>
+      </c>
       <c r="D2905" s="1" t="inlineStr">
         <is>
-          <t>讷</t>
+          <t>ni（既不；也不）</t>
         </is>
       </c>
       <c r="E2905" s="1" t="inlineStr">
@@ -93155,7 +93523,7 @@
       </c>
       <c r="B2910" s="1" t="inlineStr">
         <is>
-          <t>[repɾoduɡˈtoɾ] 玩家&lt;名&gt;</t>
+          <t>[/repɾoduɡˈtoɾ/] 播放器；复制者；生殖的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2910" s="1" t="inlineStr">
@@ -93165,7 +93533,7 @@
       </c>
       <c r="D2910" s="1" t="inlineStr">
         <is>
-          <t>玩家</t>
+          <t>播放器；复制者；生殖的</t>
         </is>
       </c>
       <c r="E2910" s="1" t="inlineStr">
@@ -93286,7 +93654,11 @@
           <t>交叉点&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2914" s="1" t="inlineStr"/>
+      <c r="C2914" s="1" t="inlineStr">
+        <is>
+          <t>/inteɾseˈkθjon/</t>
+        </is>
+      </c>
       <c r="D2914" s="1" t="inlineStr">
         <is>
           <t>交叉点</t>
@@ -93343,7 +93715,7 @@
       </c>
       <c r="B2916" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾaim] 素数&lt;名&gt;</t>
+          <t>[/ˈpɾaim/] 素数；质数&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2916" s="1" t="inlineStr">
@@ -93353,7 +93725,7 @@
       </c>
       <c r="D2916" s="1" t="inlineStr">
         <is>
-          <t>素数</t>
+          <t>素数；质数</t>
         </is>
       </c>
       <c r="E2916" s="1" t="inlineStr">
@@ -93378,7 +93750,11 @@
           <t>柴油机&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2917" s="1" t="inlineStr"/>
+      <c r="C2917" s="1" t="inlineStr">
+        <is>
+          <t>/djesel/</t>
+        </is>
+      </c>
       <c r="D2917" s="1" t="inlineStr">
         <is>
           <t>柴油机</t>
@@ -93563,7 +93939,7 @@
       </c>
       <c r="B2923" s="1" t="inlineStr">
         <is>
-          <t>[renobaˈθjon] 装修&lt;名&gt;</t>
+          <t>[/renobaˈθjon/] 更新；续期&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2923" s="1" t="inlineStr">
@@ -93573,7 +93949,7 @@
       </c>
       <c r="D2923" s="1" t="inlineStr">
         <is>
-          <t>装修</t>
+          <t>更新；续期</t>
         </is>
       </c>
       <c r="E2923" s="1" t="inlineStr">
@@ -93627,7 +94003,7 @@
       </c>
       <c r="B2925" s="1" t="inlineStr">
         <is>
-          <t>[ˈxoben] 年轻的&lt;形&gt;</t>
+          <t>[/ˈxoben/] joven 年轻的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2925" s="1" t="inlineStr">
@@ -93637,7 +94013,7 @@
       </c>
       <c r="D2925" s="1" t="inlineStr">
         <is>
-          <t>年轻的</t>
+          <t>joven 年轻的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2925" s="1" t="inlineStr">
@@ -94021,7 +94397,7 @@
       </c>
       <c r="D2937" s="1" t="inlineStr">
         <is>
-          <t>线性</t>
+          <t>线性的&lt;形&gt;（标准拼写为 lineal）</t>
         </is>
       </c>
       <c r="E2937" s="1" t="inlineStr">
@@ -94267,7 +94643,7 @@
       </c>
       <c r="B2945" s="1" t="inlineStr">
         <is>
-          <t>[ˈlao] 老挝&lt;名&gt;</t>
+          <t>[/ˈlao/] 老挝的；老挝人；老挝语&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2945" s="1" t="inlineStr">
@@ -94277,7 +94653,7 @@
       </c>
       <c r="D2945" s="1" t="inlineStr">
         <is>
-          <t>老挝</t>
+          <t>老挝的；老挝人；老挝语</t>
         </is>
       </c>
       <c r="E2945" s="1" t="inlineStr">
@@ -94331,7 +94707,7 @@
       </c>
       <c r="B2947" s="1" t="inlineStr">
         <is>
-          <t>[embeneˈnaɾ] 毒药&lt;动&gt;</t>
+          <t>[/embeneˈnaɾ/] 毒害；使中毒；下毒&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2947" s="1" t="inlineStr">
@@ -94341,7 +94717,7 @@
       </c>
       <c r="D2947" s="1" t="inlineStr">
         <is>
-          <t>毒药</t>
+          <t>毒害；使中毒；下毒</t>
         </is>
       </c>
       <c r="E2947" s="1" t="inlineStr">
@@ -94459,7 +94835,7 @@
       </c>
       <c r="B2951" s="1" t="inlineStr">
         <is>
-          <t>[ˈplei] 玩&lt;名&gt;</t>
+          <t>[/ˈplei/] 游戏；戏剧&lt;名&gt;；（体育）比赛&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2951" s="1" t="inlineStr">
@@ -94469,7 +94845,7 @@
       </c>
       <c r="D2951" s="1" t="inlineStr">
         <is>
-          <t>玩</t>
+          <t>游戏；戏剧&lt;名&gt;；（体育）比赛&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2951" s="1" t="inlineStr">
@@ -94651,7 +95027,7 @@
       </c>
       <c r="B2957" s="1" t="inlineStr">
         <is>
-          <t>[baˈkuno] 牛肉&lt;名&gt;</t>
+          <t>[/baˈkuno/] 牛的&lt;形&gt;；牛&lt;名&gt;；牛肉&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2957" s="1" t="inlineStr">
@@ -94661,7 +95037,7 @@
       </c>
       <c r="D2957" s="1" t="inlineStr">
         <is>
-          <t>牛肉</t>
+          <t>牛的&lt;形&gt;；牛&lt;名&gt;；牛肉&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2957" s="1" t="inlineStr">
@@ -95323,7 +95699,7 @@
       </c>
       <c r="B2978" s="1" t="inlineStr">
         <is>
-          <t>[aθeˈt͡ʃaɾ] 茎&lt;动&gt;</t>
+          <t>[/aθeˈt͡ʃaɾ/] 窥伺；盯梢；潜伏跟踪&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2978" s="1" t="inlineStr">
@@ -95333,7 +95709,7 @@
       </c>
       <c r="D2978" s="1" t="inlineStr">
         <is>
-          <t>茎</t>
+          <t>窥伺；盯梢；潜伏跟踪</t>
         </is>
       </c>
       <c r="E2978" s="1" t="inlineStr">
@@ -95419,7 +95795,7 @@
       </c>
       <c r="B2981" s="1" t="inlineStr">
         <is>
-          <t>[oˈtaɾ] 奥塔尔&lt;动&gt;</t>
+          <t>[/oˈtaɾ/] 祈祷；祷告&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2981" s="1" t="inlineStr">
@@ -95429,7 +95805,7 @@
       </c>
       <c r="D2981" s="1" t="inlineStr">
         <is>
-          <t>奥塔尔</t>
+          <t>祈祷；祷告</t>
         </is>
       </c>
       <c r="E2981" s="1" t="inlineStr">
@@ -95870,7 +96246,11 @@
           <t>西南&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2995" s="1" t="inlineStr"/>
+      <c r="C2995" s="1" t="inlineStr">
+        <is>
+          <t>/swoˈeste/</t>
+        </is>
+      </c>
       <c r="D2995" s="1" t="inlineStr">
         <is>
           <t>西南</t>
@@ -95991,7 +96371,7 @@
       </c>
       <c r="B2999" s="1" t="inlineStr">
         <is>
-          <t>[atoˈɾaɾ] 果酱&lt;动&gt;</t>
+          <t>[/atoˈɾaɾ/] 堵塞；卡住；阻塞&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2999" s="1" t="inlineStr">
@@ -96001,7 +96381,7 @@
       </c>
       <c r="D2999" s="1" t="inlineStr">
         <is>
-          <t>果酱</t>
+          <t>堵塞；卡住；阻塞</t>
         </is>
       </c>
       <c r="E2999" s="1" t="inlineStr">
